--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C435EE02-8D70-4126-81D7-71E8E2E13590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21EC5A2F-6787-4B37-B4A1-FDDFB97F32FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MASTER_TC" sheetId="1" r:id="rId1"/>
+    <sheet name="BUG_REPORTS" sheetId="2" r:id="rId2"/>
+    <sheet name="EXECUTION_LOG" sheetId="3" r:id="rId3"/>
+    <sheet name="DASHBOARD" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,9 +27,1519 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="458">
+  <si>
+    <t>TC ID</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>Modul</t>
+  </si>
+  <si>
+    <t>Fitur</t>
+  </si>
+  <si>
+    <t>Jenis Uji</t>
+  </si>
+  <si>
+    <t>Prioritas</t>
+  </si>
+  <si>
+    <t>Prasyarat</t>
+  </si>
+  <si>
+    <t>Langkah Uji</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Bukti</t>
+  </si>
+  <si>
+    <t>Penguji</t>
+  </si>
+  <si>
+    <t>Tanggal Uji</t>
+  </si>
+  <si>
+    <t>Commit/Build</t>
+  </si>
+  <si>
+    <t>Catatan</t>
+  </si>
+  <si>
+    <t>TC-API-001</t>
+  </si>
+  <si>
+    <t>GET List Assets</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Backend jalan, Postman siap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Buka Postman
+2. Kirim GET /api/assets 
+3. Amati response </t>
+  </si>
+  <si>
+    <t>HTTP 200, list aset tampil</t>
+  </si>
+  <si>
+    <t>Reza Tri</t>
+  </si>
+  <si>
+    <t>Test pertama — 
+BLOCKED karena backend belum jalan</t>
+  </si>
+  <si>
+    <t>TC-API-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-API-003 </t>
+  </si>
+  <si>
+    <t>TC-API-004</t>
+  </si>
+  <si>
+    <t>TC-API-005</t>
+  </si>
+  <si>
+    <t>TC-API-006</t>
+  </si>
+  <si>
+    <t>TC-API-007</t>
+  </si>
+  <si>
+    <t>TC-API-008</t>
+  </si>
+  <si>
+    <t>TC-API-009</t>
+  </si>
+  <si>
+    <t>TC-API-010</t>
+  </si>
+  <si>
+    <t>TC-API-011</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>GET Detail Asset</t>
+  </si>
+  <si>
+    <t>POST Create Asset</t>
+  </si>
+  <si>
+    <t>POST tanpa field wajib</t>
+  </si>
+  <si>
+    <t>GET ID tidak ada</t>
+  </si>
+  <si>
+    <t>PUT Update Asset</t>
+  </si>
+  <si>
+    <t>DELETE Asset</t>
+  </si>
+  <si>
+    <t>Validasi IP Address</t>
+  </si>
+  <si>
+    <t>Duplikasi Asset Code</t>
+  </si>
+  <si>
+    <t>Endpoint tanpa auth</t>
+  </si>
+  <si>
+    <t>Response time &lt; 2 detik</t>
+  </si>
+  <si>
+    <t>Negatif</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>HTTP 200, detail aset tampil</t>
+  </si>
+  <si>
+    <t>HTTP 201, aset tersimpan</t>
+  </si>
+  <si>
+    <t>HTTP 400, error jelas</t>
+  </si>
+  <si>
+    <t>HTTP 404, error jelas</t>
+  </si>
+  <si>
+    <t>HTTP 200, data terupdate</t>
+  </si>
+  <si>
+    <t>HTTP 200, aset terhapus</t>
+  </si>
+  <si>
+    <t>HTTP 409, error duplicate</t>
+  </si>
+  <si>
+    <t>HTTP 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>Response time &lt; 2000 ms</t>
+  </si>
+  <si>
+    <t>Judul</t>
+  </si>
+  <si>
+    <t>Dilaporkan oleh</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Langkah Reproduksi</t>
+  </si>
+  <si>
+    <t>Frekuensi</t>
+  </si>
+  <si>
+    <t>Dampak</t>
+  </si>
+  <si>
+    <t>PIC Perbaikan</t>
+  </si>
+  <si>
+    <t>Verified oleh</t>
+  </si>
+  <si>
+    <t>Tanggal Verifikasi</t>
+  </si>
+  <si>
+    <t>Catatan Verifikasi</t>
+  </si>
+  <si>
+    <t>BUG-001</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Staging</t>
+  </si>
+  <si>
+    <t>abc1234</t>
+  </si>
+  <si>
+    <t>Status Offline</t>
+  </si>
+  <si>
+    <t>Status masih Online</t>
+  </si>
+  <si>
+    <t>Selalu</t>
+  </si>
+  <si>
+    <t>Monitoring tidak akurat</t>
+  </si>
+  <si>
+    <t>screenshots/BUG-001.png</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Ananda</t>
+  </si>
+  <si>
+    <t>Menunggu perbaikan</t>
+  </si>
+  <si>
+    <t>BUG-002</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>HTTP 500</t>
+  </si>
+  <si>
+    <t>Update aset tidak bisa</t>
+  </si>
+  <si>
+    <t>screenshots/BUG-002.png</t>
+  </si>
+  <si>
+    <t>Ahmad Reza</t>
+  </si>
+  <si>
+    <t>Menunggu fix</t>
+  </si>
+  <si>
+    <t>1. ESP32 online 
+2. Matikan 
+3. Tunggu 6 menit 
+4. Refresh dashboard</t>
+  </si>
+  <si>
+    <t>1. PUT /api/assets/AST-001 
+2. Body valid 
+3. Amati response</t>
+  </si>
+  <si>
+    <t>Status device tetap Online 
+padahal ESP32 mati</t>
+  </si>
+  <si>
+    <t>Endpoint PUT 500 Internal 
+Server Error</t>
+  </si>
+  <si>
+    <t>Hari ke-</t>
+  </si>
+  <si>
+    <t>Shift</t>
+  </si>
+  <si>
+    <t>Total TC</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
+    <t>Bug Baru</t>
+  </si>
+  <si>
+    <t>Bug Verified</t>
+  </si>
+  <si>
+    <t>Link Test Report</t>
+  </si>
+  <si>
+    <t>Shift 2</t>
+  </si>
+  <si>
+    <t>Setup QA &amp; Docs, blocker backend</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-11_Hari-1.md</t>
+  </si>
+  <si>
+    <t>Susun test case tambahan</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-12_Hari-2.md</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Validasi test case dengan Damar</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-13_Hari-3.md</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>Review acceptance criteria</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-14_Hari-4.md</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>Review architecture</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-15_Hari-5.md</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>Uji schema database</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-16_Hari-6.md</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>Test checklist wireframe</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-17_Hari-7.md</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>API dasar + smoke test</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-18_Hari-8.md</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>API validation</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-19_Hari-9.md</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>Smoke test MVP</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-20_Hari-10.md</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>Monitoring engine</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-21_Hari-11.md</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>Retry logic</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-22_Hari-12.md</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>Heartbeat normal</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-23_Hari-13.md</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>Reconnect test</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-24_Hari-14.md</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>Dashboard utama</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-25_Hari-15.md</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
+    <t>List &amp; filter</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-26_Hari-16.md</t>
+  </si>
+  <si>
+    <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>Detail device</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-27_Hari-17.md</t>
+  </si>
+  <si>
+    <t>28/10/2026</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-28_Hari-18.md</t>
+  </si>
+  <si>
+    <t>29/10/2026</t>
+  </si>
+  <si>
+    <t>Uptime/downtime</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-29_Hari-19.md</t>
+  </si>
+  <si>
+    <t>30/10/2026</t>
+  </si>
+  <si>
+    <t>MVP release</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-30_Hari-20.md</t>
+  </si>
+  <si>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>Offline alert</t>
+  </si>
+  <si>
+    <t>test-reports/2026-10-31_Hari-21.md</t>
+  </si>
+  <si>
+    <t>Recovery alert</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-01_Hari-22.md</t>
+  </si>
+  <si>
+    <t>Map/location</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-02_Hari-23.md</t>
+  </si>
+  <si>
+    <t>AI automation</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-03_Hari-24.md</t>
+  </si>
+  <si>
+    <t>Reporting</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-04_Hari-25.md</t>
+  </si>
+  <si>
+    <t>Security test</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-05_Hari-26.md</t>
+  </si>
+  <si>
+    <t>Failure simulation</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-06_Hari-27.md</t>
+  </si>
+  <si>
+    <t>Regression test</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-07_Hari-28.md</t>
+  </si>
+  <si>
+    <t>Dokumentasi</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-08_Hari-29.md</t>
+  </si>
+  <si>
+    <t>Final demo</t>
+  </si>
+  <si>
+    <t>test-reports/2026-11-09_Hari-30.md</t>
+  </si>
+  <si>
+    <t>% Progress</t>
+  </si>
+  <si>
+    <t>Device Monitoring</t>
+  </si>
+  <si>
+    <t>Last Seen</t>
+  </si>
+  <si>
+    <t>Response Time</t>
+  </si>
+  <si>
+    <t>Monitoring History</t>
+  </si>
+  <si>
+    <t>Uptime / Downtime</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>User Management</t>
+  </si>
+  <si>
+    <t>AI Automation</t>
+  </si>
+  <si>
+    <t>TC-ASSET-001</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>Bearer token, aset terdaftar</t>
+  </si>
+  <si>
+    <t>TC-ASSET-002</t>
+  </si>
+  <si>
+    <t>Bearer token</t>
+  </si>
+  <si>
+    <t>TC-ASSET-003</t>
+  </si>
+  <si>
+    <t>200, category Access Point, monitoring_method Ping/SNMP</t>
+  </si>
+  <si>
+    <t>TC-ASSET-004</t>
+  </si>
+  <si>
+    <t>TC-ASSET-005</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Firewall pfSense</t>
+  </si>
+  <si>
+    <t>TC-ASSET-006</t>
+  </si>
+  <si>
+    <t>TC-ASSET-007</t>
+  </si>
+  <si>
+    <t>Verifikasi aset IoT Node ESP32</t>
+  </si>
+  <si>
+    <t>TC-ASSET-008</t>
+  </si>
+  <si>
+    <t>Verifikasi aset CCTV Head Office</t>
+  </si>
+  <si>
+    <t>200, category CCTV, monitoring_method Ping + HTTP</t>
+  </si>
+  <si>
+    <t>TC-ASSET-009</t>
+  </si>
+  <si>
+    <t>Verifikasi aset PC Head Office 01</t>
+  </si>
+  <si>
+    <t>200, category PC, monitoring_method Ping</t>
+  </si>
+  <si>
+    <t>TC-ASSET-010</t>
+  </si>
+  <si>
+    <t>Filter by category Router</t>
+  </si>
+  <si>
+    <t>200, hanya Router yang tampil</t>
+  </si>
+  <si>
+    <t>TC-ASSET-011</t>
+  </si>
+  <si>
+    <t>Filter by category IoT Node</t>
+  </si>
+  <si>
+    <t>200, hanya IoT Node (ESP32, RPi) tampil</t>
+  </si>
+  <si>
+    <t>TC-ASSET-012</t>
+  </si>
+  <si>
+    <t>Filter by location Head Office</t>
+  </si>
+  <si>
+    <t>200, hanya aset di Head Office</t>
+  </si>
+  <si>
+    <t>TC-ASSET-013</t>
+  </si>
+  <si>
+    <t>Verifikasi IP MikroTik 192.168.10.1</t>
+  </si>
+  <si>
+    <t>200, ip_address = 192.168.10.1</t>
+  </si>
+  <si>
+    <t>TC-ASSET-014</t>
+  </si>
+  <si>
+    <t>200, mqtt_topic = taims/heartbeat/IOT-ESP-01</t>
+  </si>
+  <si>
+    <t>TC-ASSET-015</t>
+  </si>
+  <si>
+    <t>Verifikasi priority aset kritis = 1</t>
+  </si>
+  <si>
+    <t>200, semua aset priority 1 tampil</t>
+  </si>
+  <si>
+    <t>TC-INC-001</t>
+  </si>
+  <si>
+    <t>Incidents</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
+    <t>Kabel uplink siap dicabut</t>
+  </si>
+  <si>
+    <t>TC-INC-002</t>
+  </si>
+  <si>
+    <t>Kabel siap dicolok kembali</t>
+  </si>
+  <si>
+    <t>TC-INC-003</t>
+  </si>
+  <si>
+    <t>Kabel WAN siap dicabut</t>
+  </si>
+  <si>
+    <t>Status offline, incident type "Connection Loss", severity high</t>
+  </si>
+  <si>
+    <t>TC-INC-004</t>
+  </si>
+  <si>
+    <t>RPi terpasang adaptor</t>
+  </si>
+  <si>
+    <t>TC-INC-005</t>
+  </si>
+  <si>
+    <t>ESP32 terpasang USB</t>
+  </si>
+  <si>
+    <t>Status offline, LWT MQTT trigger offline</t>
+  </si>
+  <si>
+    <t>TC-INC-006</t>
+  </si>
+  <si>
+    <t>Server bisa di-restart</t>
+  </si>
+  <si>
+    <t>TC-INC-007</t>
+  </si>
+  <si>
+    <t>ESP32 siap dinyalakan</t>
+  </si>
+  <si>
+    <t>TC-INC-008</t>
+  </si>
+  <si>
+    <t>Ada incident dari simulasi</t>
+  </si>
+  <si>
+    <t>TC-INC-009</t>
+  </si>
+  <si>
+    <t>Update incident status resolved</t>
+  </si>
+  <si>
+    <t>Ada incident open</t>
+  </si>
+  <si>
+    <t>200, incident_status = resolved</t>
+  </si>
+  <si>
+    <t>TC-INC-010</t>
+  </si>
+  <si>
+    <t>MQTT &amp; Telegram aktif</t>
+  </si>
+  <si>
+    <t>TC-INC-011</t>
+  </si>
+  <si>
+    <t>Notifikasi recovery terkirim</t>
+  </si>
+  <si>
+    <t>1. Sambung kabel 2. Cek Telegram</t>
+  </si>
+  <si>
+    <t>Recovery alert terkirim setelah status online</t>
+  </si>
+  <si>
+    <t>TC-INC-012</t>
+  </si>
+  <si>
+    <t>Cooldown 5 menit</t>
+  </si>
+  <si>
+    <t>Hanya 1 alert offline + 1 alert recovery</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code NET-RTR-01 
+3. Cek field lengkap</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code NET-SWD-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code NET-AP-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code SRV-TAIMS-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code NET-FW-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code STO-NAS-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code IOT-ESP-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets 
+2. Cari asset_code SEC-CCTV-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets
+ 2. Cari asset_code PC-HO-01 
+3. Cek detail</t>
+  </si>
+  <si>
+    <t>1. GET /assets?category=Router 
+2. Cek hasil</t>
+  </si>
+  <si>
+    <t>1. GET /assets?category=IoT Node 
+2. Cek hasil</t>
+  </si>
+  <si>
+    <t>1. GET /assets?location_id=2 
+2. Cek hasil</t>
+  </si>
+  <si>
+    <t>1. GET /assets/NET-RTR-01 
+2. Cek field ip_address</t>
+  </si>
+  <si>
+    <t>1. GET /assets/IOT-ESP-01 
+2. Cek monitoring_config.mqtt_topic</t>
+  </si>
+  <si>
+    <t>1. GET /assets?priority=1 
+2. Cek hasil</t>
+  </si>
+  <si>
+    <t>1. Sambung kabel LAN 
+2. Tunggu heartbeat 
+3. Cek status</t>
+  </si>
+  <si>
+    <t>1. Catat status awal switch 
+2. Cabut kabel LAN uplink
+3. Tunggu threshold 
+4. Cek status di API</t>
+  </si>
+  <si>
+    <t>1. Catat status 
+2. Cabut kabel WAN 
+3. Cek monitoring</t>
+  </si>
+  <si>
+    <t>1. Cabut adaptor power RPi 
+2. Tunggu 90 detik
+ 3. Cek API status</t>
+  </si>
+  <si>
+    <t>1. Cabut USB power ESP32 
+2. Tunggu 90 detik 
+3. Cek API</t>
+  </si>
+  <si>
+    <t>1. Matikan server 
+2. Cek dari laptop lain 
+3. Cek HTTP health check</t>
+  </si>
+  <si>
+    <t>1. Nyalakan ESP32 
+2. Tunggu heartbeat kirim 
+3. Cek status</t>
+  </si>
+  <si>
+    <t>1. GET /incidents?status=open 
+2. Cek field</t>
+  </si>
+  <si>
+    <t>1. PUT /incidents/:id 
+2. Body status=resolved
+ 3. Cek response</t>
+  </si>
+  <si>
+    <t>1. Cabut-nyambung kabel 3x dalam 2 menit 
+2. Cek Telegram</t>
+  </si>
+  <si>
+    <t>200, data: asset_code, asset_name,
+ category Router, ip_address,
+ monitoring_method Ping</t>
+  </si>
+  <si>
+    <t>200, category Switch Manageable,
+ monitoring_method Ping/SNMP</t>
+  </si>
+  <si>
+    <t>200, category Storage,
+monitoring_method Ping</t>
+  </si>
+  <si>
+    <t>200, category Server,
+monitoring_method HTTP</t>
+  </si>
+  <si>
+    <t>200, category Firewall,
+monitoring_method Ping</t>
+  </si>
+  <si>
+    <t>200, category IoT Node, monitoring_method Heartbeat, 
+monitoring_config mqtt_topic</t>
+  </si>
+  <si>
+    <t>Status berubah offline, 
+incident tercatat, notifikasi terkirim</t>
+  </si>
+  <si>
+    <t>Status kembali online, 
+incident resolved, recovery alert terkirim</t>
+  </si>
+  <si>
+    <t>Status offline, last_seen stop, 
+heartbeat berhenti</t>
+  </si>
+  <si>
+    <t>HTTP check gagal, status offline, 
+incident critical</t>
+  </si>
+  <si>
+    <t>200, incident dengan detected_at, 
+severity, incident_status</t>
+  </si>
+  <si>
+    <t>Status online, recovery alert terkirim, 
+last_seen update</t>
+  </si>
+  <si>
+    <t>Alert diterima dalam 90 detik,
+ isi device_code + waktu</t>
+  </si>
+  <si>
+    <t>TC-AUTH-001</t>
+  </si>
+  <si>
+    <t>Auth</t>
+  </si>
+  <si>
+    <t>Login sukses dengan kredensial valid</t>
+  </si>
+  <si>
+    <t>Contract API v0.5</t>
+  </si>
+  <si>
+    <t>200 OK, token + user data</t>
+  </si>
+  <si>
+    <t>TC-AUTH-002</t>
+  </si>
+  <si>
+    <t>Login gagal - password salah</t>
+  </si>
+  <si>
+    <t>401, error password salah</t>
+  </si>
+  <si>
+    <t>TC-AUTH-003</t>
+  </si>
+  <si>
+    <t>Login tanpa email/password</t>
+  </si>
+  <si>
+    <t>400, error wajib diisi</t>
+  </si>
+  <si>
+    <t>TC-AUTH-004</t>
+  </si>
+  <si>
+    <t>GET /auth/me dengan token valid</t>
+  </si>
+  <si>
+    <t>Login dulu</t>
+  </si>
+  <si>
+    <t>200, data user login</t>
+  </si>
+  <si>
+    <t>TC-AUTH-005</t>
+  </si>
+  <si>
+    <t>GET /auth/me tanpa token</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-AUTH-006</t>
+  </si>
+  <si>
+    <t>Change password berhasil</t>
+  </si>
+  <si>
+    <t>200, password berubah</t>
+  </si>
+  <si>
+    <t>TC-USER-001</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>GET /users sebagai admin</t>
+  </si>
+  <si>
+    <t>Bearer admin</t>
+  </si>
+  <si>
+    <t>200, list user</t>
+  </si>
+  <si>
+    <t>TC-USER-002</t>
+  </si>
+  <si>
+    <t>GET /users sebagai user (403)</t>
+  </si>
+  <si>
+    <t>Bearer user</t>
+  </si>
+  <si>
+    <t>403 Forbidden</t>
+  </si>
+  <si>
+    <t>TC-USER-003</t>
+  </si>
+  <si>
+    <t>POST create user</t>
+  </si>
+  <si>
+    <t>201, user_id baru</t>
+  </si>
+  <si>
+    <t>TC-USER-004</t>
+  </si>
+  <si>
+    <t>POST email duplikat (409)</t>
+  </si>
+  <si>
+    <t>409 Conflict</t>
+  </si>
+  <si>
+    <t>TC-USER-005</t>
+  </si>
+  <si>
+    <t>DELETE user sebagai admin (403)</t>
+  </si>
+  <si>
+    <t>TC-LOC-001</t>
+  </si>
+  <si>
+    <t>Locations</t>
+  </si>
+  <si>
+    <t>GET list lokasi</t>
+  </si>
+  <si>
+    <t>200, 2 lokasi (HO, Marketing)</t>
+  </si>
+  <si>
+    <t>TC-LOC-002</t>
+  </si>
+  <si>
+    <t>POST create lokasi</t>
+  </si>
+  <si>
+    <t>201 Created</t>
+  </si>
+  <si>
+    <t>TC-LOC-003</t>
+  </si>
+  <si>
+    <t>DELETE lokasi dipakai (409)</t>
+  </si>
+  <si>
+    <t>Bearer super_admin</t>
+  </si>
+  <si>
+    <t>TC-MON-001</t>
+  </si>
+  <si>
+    <t>POST /monitoring/ping</t>
+  </si>
+  <si>
+    <t>Ananda engine</t>
+  </si>
+  <si>
+    <t>201, log_id</t>
+  </si>
+  <si>
+    <t>TC-MON-002</t>
+  </si>
+  <si>
+    <t>POST /monitoring/http</t>
+  </si>
+  <si>
+    <t>TC-MON-003</t>
+  </si>
+  <si>
+    <t>POST /monitoring/tcp</t>
+  </si>
+  <si>
+    <t>TC-MON-004</t>
+  </si>
+  <si>
+    <t>GET monitoring logs</t>
+  </si>
+  <si>
+    <t>200, list log</t>
+  </si>
+  <si>
+    <t>TC-MON-005</t>
+  </si>
+  <si>
+    <t>GET monitoring summary</t>
+  </si>
+  <si>
+    <t>200, ringkasan status</t>
+  </si>
+  <si>
+    <t>TC-HB-001</t>
+  </si>
+  <si>
+    <t>Heartbeat</t>
+  </si>
+  <si>
+    <t>POST heartbeat valid</t>
+  </si>
+  <si>
+    <t>Device terdaftar</t>
+  </si>
+  <si>
+    <t>200, next_heartbeat_in</t>
+  </si>
+  <si>
+    <t>TC-HB-002</t>
+  </si>
+  <si>
+    <t>POST device_id tidak terdaftar</t>
+  </si>
+  <si>
+    <t>404, error device_id tidak terdaftar</t>
+  </si>
+  <si>
+    <t>TC-HB-003</t>
+  </si>
+  <si>
+    <t>GET heartbeat terakhir</t>
+  </si>
+  <si>
+    <t>200, data heartbeat</t>
+  </si>
+  <si>
+    <t>TC-MNT-001</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>GET list maintenance</t>
+  </si>
+  <si>
+    <t>200, list maintenance</t>
+  </si>
+  <si>
+    <t>TC-MNT-002</t>
+  </si>
+  <si>
+    <t>POST create maintenance</t>
+  </si>
+  <si>
+    <t>201, maintenance_id</t>
+  </si>
+  <si>
+    <t>TC-NOTIF-001</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>GET list notifikasi</t>
+  </si>
+  <si>
+    <t>200, list notifikasi</t>
+  </si>
+  <si>
+    <t>TC-NOTIF-002</t>
+  </si>
+  <si>
+    <t>PUT mark as read</t>
+  </si>
+  <si>
+    <t>200, is_read=true</t>
+  </si>
+  <si>
+    <t>TC-NOTIF-003</t>
+  </si>
+  <si>
+    <t>POST create notifikasi</t>
+  </si>
+  <si>
+    <t>201, notification_id</t>
+  </si>
+  <si>
+    <t>TC-DASH-001</t>
+  </si>
+  <si>
+    <t>GET dashboard stats</t>
+  </si>
+  <si>
+    <t>200, total/online/offline</t>
+  </si>
+  <si>
+    <t>TC-DASH-002</t>
+  </si>
+  <si>
+    <t>GET dashboard uptime</t>
+  </si>
+  <si>
+    <t>200, uptime per device</t>
+  </si>
+  <si>
+    <t>TC-DASH-003</t>
+  </si>
+  <si>
+    <t>GET dashboard top-issues</t>
+  </si>
+  <si>
+    <t>200, device bermasalah</t>
+  </si>
+  <si>
+    <t>TC-DASH-004</t>
+  </si>
+  <si>
+    <t>GET dashboard charts</t>
+  </si>
+  <si>
+    <t>200, data grafik</t>
+  </si>
+  <si>
+    <t>TC-DASH-005</t>
+  </si>
+  <si>
+    <t>GET dashboard AI report</t>
+  </si>
+  <si>
+    <t>200, summary + recommendation</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Router 
+MikroTik RB4011 terdaftar</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Switch 
+Cisco 2960 terdaftar</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Access 
+Point UniFi U6-Lite</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Server 
+T-AIMS Ubuntu</t>
+  </si>
+  <si>
+    <t>Verifikasi aset Storage 
+Synology DS220+</t>
+  </si>
+  <si>
+    <t>Verifikasi monitoring_config 
+ESP32 mqtt_topic</t>
+  </si>
+  <si>
+    <t>Simulasi KABEL PUTUS - 
+Switch Cisco</t>
+  </si>
+  <si>
+    <t>Simulasi KABEL PUTUS - 
+Recovery</t>
+  </si>
+  <si>
+    <t>Simulasi KABEL PUTUS - 
+Router MikroTik</t>
+  </si>
+  <si>
+    <t>Simulasi POWER CUT - 
+Raspberry Pi</t>
+  </si>
+  <si>
+    <t>Simulasi POWER CUT - 
+ESP32</t>
+  </si>
+  <si>
+    <t>Simulasi POWER CUT - 
+Server T-AIMS</t>
+  </si>
+  <si>
+    <t>Simulasi POWER CUT - 
+Recovery ESP32</t>
+  </si>
+  <si>
+    <t>Verifikasi incident tercatat 
+di database</t>
+  </si>
+  <si>
+    <t>Notifikasi offline terkirim 
+saat kabel putus</t>
+  </si>
+  <si>
+    <t>Tidak ada duplikasi alert 
+saat flapping</t>
+  </si>
+  <si>
+    <t>1. Cabut kabel 
+2. Cek Telegram/Email</t>
+  </si>
+  <si>
+    <t>1. POST /auth/login 
+2. Body valid 
+3. Amati response</t>
+  </si>
+  <si>
+    <t>1. POST /auth/login 
+2. Password salah 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /auth/login 
+2. Body kosong 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /auth/me 
+2. Bearer token 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /auth/me 
+2. Tanpa auth 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /auth/change-password 
+2. Body old+new 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /users 
+2. Amati response</t>
+  </si>
+  <si>
+    <t>1. POST /users 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /users 
+2. Email sudah ada 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. DELETE /users/:id 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /locations 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /locations 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. DELETE /locations/:id (ada aset) 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /monitoring/ping 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /monitoring/http 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /monitoring/tcp 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /monitoring/logs 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /monitoring/summary 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /heartbeat 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /heartbeat 
+2. device_id salah 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /heartbeat/:assetCode/latest 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /maintenance 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /maintenance 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /notifications 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. PUT /notifications/:id/read 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. POST /notifications 
+2. Body valid 
+3. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /dashboard/stats 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /dashboard/uptime 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /dashboard/top-issues 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /dashboard/charts 
+2. Amati</t>
+  </si>
+  <si>
+    <t>1. GET /dashboard/ai-report 
+2. Amati</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -34,13 +1547,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,14 +1586,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -371,9 +1951,4451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD110E8-1ACA-4357-B4C2-32B0031F67AE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="38.453125" customWidth="1"/>
+    <col min="5" max="6" width="10.36328125" customWidth="1"/>
+    <col min="7" max="7" width="25.26953125" customWidth="1"/>
+    <col min="8" max="8" width="57.7265625" customWidth="1"/>
+    <col min="9" max="9" width="97.36328125" customWidth="1"/>
+    <col min="10" max="10" width="20.7265625" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" customWidth="1"/>
+    <col min="13" max="14" width="10.36328125" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" customWidth="1"/>
+    <col min="16" max="16" width="16.90625" customWidth="1"/>
+    <col min="17" max="17" width="18.1796875" customWidth="1"/>
+    <col min="18" max="18" width="28.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="18">
+        <v>8</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="18">
+        <v>8</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="11"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="18">
+        <v>8</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="11"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="18">
+        <v>8</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="18">
+        <v>9</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="11"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="18">
+        <v>9</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="18">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="18">
+        <v>9</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="11"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="18">
+        <v>9</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="11"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="18">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="18">
+        <v>13</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="18">
+        <v>13</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="18">
+        <v>13</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="I15" t="s">
+        <v>203</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="18">
+        <v>13</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="18">
+        <v>13</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="18">
+        <v>13</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="18">
+        <v>13</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" s="18">
+        <v>13</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I20" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="18">
+        <v>13</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I21" t="s">
+        <v>215</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="18">
+        <v>13</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" t="s">
+        <v>218</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="18">
+        <v>13</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" t="s">
+        <v>221</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="18">
+        <v>13</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" t="s">
+        <v>224</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="18">
+        <v>13</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I25" t="s">
+        <v>227</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26" s="18">
+        <v>13</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="I26" t="s">
+        <v>229</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B27" s="18">
+        <v>13</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" t="s">
+        <v>232</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="18">
+        <v>27</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B29" s="18">
+        <v>27</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="18">
+        <v>27</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="I30" t="s">
+        <v>241</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="18">
+        <v>27</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B32" s="18">
+        <v>27</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="I32" t="s">
+        <v>246</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="18">
+        <v>27</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="18">
+        <v>27</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B35" s="18">
+        <v>27</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B36" s="18">
+        <v>27</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="I36" t="s">
+        <v>256</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="18">
+        <v>27</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B38" s="18">
+        <v>27</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H38" t="s">
+        <v>261</v>
+      </c>
+      <c r="I38" t="s">
+        <v>262</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="18">
+        <v>27</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" t="s">
+        <v>265</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B40" s="18">
+        <v>8</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="O40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P40" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B41" s="18">
+        <v>8</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="O41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P41" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B42" s="18">
+        <v>8</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="O42" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P42" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B43" s="18">
+        <v>8</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="O43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="B44" s="18">
+        <v>8</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="O44" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P44" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" s="18">
+        <v>8</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="O45" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P45" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B46" s="18">
+        <v>9</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="O46" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" s="18">
+        <v>9</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="O47" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P47" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B48" s="18">
+        <v>9</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="O48" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P48" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B49" s="18">
+        <v>9</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="O49" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P49" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B50" s="18">
+        <v>9</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="O50" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P50" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" s="18">
+        <v>10</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="O51" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P51" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B52" s="18">
+        <v>10</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="O52" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B53" s="18">
+        <v>10</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="O53" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P53" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B54" s="18">
+        <v>11</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="O54" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B55" s="18">
+        <v>11</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="K55" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="O55" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P55" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B56" s="18">
+        <v>11</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="O56" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B57" s="18">
+        <v>11</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="O57" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P57" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B58" s="18">
+        <v>11</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="O58" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P58" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B59" s="18">
+        <v>13</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="O59" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B60" s="18">
+        <v>13</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="O60" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P60" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B61" s="18">
+        <v>13</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="O61" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B62" s="18">
+        <v>17</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="K62" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="O62" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B63" s="18">
+        <v>17</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="O63" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P63" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B64" s="18">
+        <v>21</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="O64" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P64" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B65" s="18">
+        <v>21</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="O65" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P65" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B66" s="18">
+        <v>21</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="O66" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P66" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B67" s="18">
+        <v>15</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="O67" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P67" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B68" s="18">
+        <v>19</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="K68" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="O68" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P68" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B69" s="18">
+        <v>19</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="O69" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P69" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="B70" s="18">
+        <v>15</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="K70" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="O70" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P70" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B71" s="18">
+        <v>24</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="O71" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P71" s="13">
+        <v>46366</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A87AFD-E38E-4752-8345-B70DBD79E2D9}">
+  <dimension ref="A1:W3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="26.08984375" customWidth="1"/>
+    <col min="11" max="11" width="23.7265625" customWidth="1"/>
+    <col min="12" max="12" width="19.08984375" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="23.26953125" customWidth="1"/>
+    <col min="15" max="15" width="26.08984375" customWidth="1"/>
+    <col min="16" max="16" width="8.453125" customWidth="1"/>
+    <col min="17" max="17" width="13.81640625" customWidth="1"/>
+    <col min="18" max="18" width="14.26953125" customWidth="1"/>
+    <col min="19" max="19" width="17.453125" customWidth="1"/>
+    <col min="20" max="20" width="18.36328125" customWidth="1"/>
+    <col min="21" max="21" width="21.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="13">
+        <v>46336</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+    </row>
+    <row r="3" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="13">
+        <v>46336</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEC8255-0EEE-4423-BFD7-EF6029BE1B7F}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+    <col min="9" max="9" width="9.26953125" customWidth="1"/>
+    <col min="10" max="10" width="12.1796875" customWidth="1"/>
+    <col min="11" max="11" width="29.7265625" customWidth="1"/>
+    <col min="12" max="12" width="32.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="13">
+        <v>46336</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <v>46366</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>109</v>
+      </c>
+      <c r="L3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="6">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="6">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="6">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="6">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="6">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="6">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="6">
+        <v>5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="6">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>133</v>
+      </c>
+      <c r="L11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="6">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>136</v>
+      </c>
+      <c r="L12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="6">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="6">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>5</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="6">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>145</v>
+      </c>
+      <c r="L15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="6">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="6">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6">
+        <v>5</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>148</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="6">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="6">
+        <v>5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>151</v>
+      </c>
+      <c r="L17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="6">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="6">
+        <v>4</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>154</v>
+      </c>
+      <c r="L18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="6">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="6">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="6">
+        <v>4</v>
+      </c>
+      <c r="E20" s="6">
+        <v>4</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>160</v>
+      </c>
+      <c r="L20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="6">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="6">
+        <v>6</v>
+      </c>
+      <c r="E21" s="6">
+        <v>5</v>
+      </c>
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" s="6">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4</v>
+      </c>
+      <c r="E22" s="6">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>166</v>
+      </c>
+      <c r="L22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46033</v>
+      </c>
+      <c r="B23" s="6">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="6">
+        <v>4</v>
+      </c>
+      <c r="E23" s="6">
+        <v>4</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>168</v>
+      </c>
+      <c r="L23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46064</v>
+      </c>
+      <c r="B24" s="6">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6">
+        <v>4</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46092</v>
+      </c>
+      <c r="B25" s="6">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="6">
+        <v>5</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>172</v>
+      </c>
+      <c r="L25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46123</v>
+      </c>
+      <c r="B26" s="6">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="6">
+        <v>4</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>174</v>
+      </c>
+      <c r="L26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46153</v>
+      </c>
+      <c r="B27" s="6">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="6">
+        <v>9</v>
+      </c>
+      <c r="E27" s="6">
+        <v>7</v>
+      </c>
+      <c r="F27" s="6">
+        <v>2</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
+        <v>2</v>
+      </c>
+      <c r="J27" s="6">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>176</v>
+      </c>
+      <c r="L27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46184</v>
+      </c>
+      <c r="B28" s="6">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6">
+        <v>6</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>178</v>
+      </c>
+      <c r="L28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46214</v>
+      </c>
+      <c r="B29" s="6">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="6">
+        <v>4</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>180</v>
+      </c>
+      <c r="L29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B30" s="6">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="6">
+        <v>5</v>
+      </c>
+      <c r="E30" s="6">
+        <v>5</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6">
+        <v>0</v>
+      </c>
+      <c r="J30" s="6">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>182</v>
+      </c>
+      <c r="L30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="6">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="6">
+        <v>6</v>
+      </c>
+      <c r="E31" s="6">
+        <v>6</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463636D4-2B56-4AA6-9F40-79E1FF7345CF}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A2)</f>
+        <v>11</v>
+      </c>
+      <c r="C2" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="15">
+        <f>IFERROR(C2/B2,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A3)</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <f>IF(B3=0,0,C3/B3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A4)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>IF(B4=0,0,C4/B4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A5)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <f>IF(B5=0,0,C5/B5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A6)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <f>IF(B6=0,0,C6/B6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <f>IF(B7=0,0,C7/B7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A8)</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"PASS")</f>
+        <v>5</v>
+      </c>
+      <c r="D8" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <f>IF(B8=0,0,C8/B8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A10)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f>IF(B10=0,0,C10/B10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A11)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f>IF(B11=0,0,C11/B11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f>IF(B12=0,0,C12/B12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="6">
+        <f>COUNTIF(MASTER_TC!C:C,A13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"BLOCKED")</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>IF(B13=0,0,C13/B13)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD85B9E8-78B5-4181-8848-99AB5F6E22B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E515C53D-F16C-4A05-80CB-ECB3B25F6DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER_TC" sheetId="1" r:id="rId1"/>
-    <sheet name="BUG_REPORTS" sheetId="2" r:id="rId2"/>
-    <sheet name="EXECUTION_LOG" sheetId="3" r:id="rId3"/>
-    <sheet name="DASHBOARD" sheetId="4" r:id="rId4"/>
+    <sheet name="BUG_LIST_DZAKWAN" sheetId="5" r:id="rId2"/>
+    <sheet name="BUG_REPORTS" sheetId="2" r:id="rId3"/>
+    <sheet name="EXECUTION_LOG" sheetId="3" r:id="rId4"/>
+    <sheet name="DASHBOARD" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="467">
   <si>
     <t>TC ID</t>
   </si>
@@ -1540,6 +1541,30 @@
     <t>1. GET /assets 
 2. Cari asset_code SRV-MQTT-01 
 3. Cek detail</t>
+  </si>
+  <si>
+    <t>ID Bug</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>BUG-003</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Field asset_code bisa 
+dikosongkan saat POST</t>
+  </si>
+  <si>
+    <t>Token JWT tidak expire 
+setelah logout</t>
+  </si>
+  <si>
+    <t>Response time tidak 
+tercatat saat ping timeout</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1622,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1616,6 +1641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1642,6 +1668,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2066,10 +2098,10 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="12"/>
+      <c r="O2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="20"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="4" t="s">
         <v>26</v>
@@ -2079,1243 +2111,1243 @@
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <v>8</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="11"/>
+      <c r="O3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="20"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <v>8</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="11"/>
+      <c r="O4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="20"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <v>8</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I5" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="11"/>
+      <c r="O5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <v>8</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I6" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="11"/>
+      <c r="O6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="20"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <v>9</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I7" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="11"/>
+      <c r="O7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <v>9</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="11"/>
+      <c r="O8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="20"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <v>9</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="11"/>
+      <c r="O9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I10" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10" s="11"/>
+      <c r="O10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="20"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <v>9</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>21</v>
       </c>
       <c r="I11" t="s">
         <v>58</v>
       </c>
-      <c r="O11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="11"/>
+      <c r="O11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="20"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>10</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="18" t="s">
         <v>50</v>
       </c>
       <c r="I12" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12" s="11"/>
+      <c r="O12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="20"/>
     </row>
     <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>13</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="O13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <v>13</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="O14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>265</v>
       </c>
       <c r="I15" t="s">
         <v>203</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="K15" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="O15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <v>13</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="O16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="19">
         <v>13</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="O17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="19">
         <v>13</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P18" s="13">
+      <c r="O18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <v>13</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O19" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="O19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <v>13</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>459</v>
       </c>
       <c r="I20" t="s">
         <v>458</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="O20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <v>13</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>268</v>
       </c>
       <c r="I21" t="s">
         <v>212</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="O21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="19">
         <v>13</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>269</v>
       </c>
       <c r="I22" t="s">
         <v>215</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O22" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="O22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="19">
         <v>13</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>270</v>
       </c>
       <c r="I23" t="s">
         <v>218</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O23" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="O23" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="19">
         <v>13</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>271</v>
       </c>
       <c r="I24" t="s">
         <v>221</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O24" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24" s="13">
+      <c r="O24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="19">
         <v>13</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>272</v>
       </c>
       <c r="I25" t="s">
         <v>224</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="K25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O25" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="O25" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="19">
         <v>13</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>273</v>
       </c>
       <c r="I26" t="s">
         <v>226</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="K26" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O26" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="13">
+      <c r="O26" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <v>13</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>274</v>
       </c>
       <c r="I27" t="s">
         <v>229</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="K27" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O27" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="O27" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="19">
         <v>27</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="K28" s="12" t="s">
+      <c r="K28" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O28" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28" s="12" t="s">
+      <c r="O28" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="19">
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O29" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P29" s="12" t="s">
+      <c r="O29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <v>27</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>277</v>
       </c>
       <c r="I30" t="s">
         <v>238</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O30" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P30" s="12" t="s">
+      <c r="O30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P30" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="19">
         <v>27</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O31" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P31" s="12" t="s">
+      <c r="O31" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P31" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="19">
         <v>27</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="11" t="s">
         <v>279</v>
       </c>
       <c r="I32" t="s">
         <v>243</v>
       </c>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O32" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32" s="12" t="s">
+      <c r="O32" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="19">
         <v>27</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O33" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P33" s="12" t="s">
+      <c r="O33" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="19">
         <v>27</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K34" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O34" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P34" s="12" t="s">
+      <c r="O34" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P34" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="19">
         <v>27</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K35" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O35" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P35" s="12" t="s">
+      <c r="O35" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P35" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="19">
         <v>27</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>283</v>
       </c>
       <c r="I36" t="s">
         <v>253</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P36" s="12" t="s">
+      <c r="O36" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="19">
         <v>27</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K37" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P37" s="12" t="s">
+      <c r="O37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="19">
         <v>27</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="13" t="s">
         <v>255</v>
       </c>
       <c r="H38" t="s">
@@ -3324,1331 +3356,1331 @@
       <c r="I38" t="s">
         <v>259</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P38" s="12" t="s">
+      <c r="O38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P38" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="19">
         <v>27</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>284</v>
       </c>
       <c r="I39" t="s">
         <v>262</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="O39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P39" s="12" t="s">
+      <c r="O39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P39" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="19">
         <v>8</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="H40" s="14" t="s">
+      <c r="H40" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="O40" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P40" s="13">
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="O40" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P40" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="19">
         <v>8</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="K41" s="12" t="s">
+      <c r="K41" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="O41" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P41" s="13">
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="O41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P41" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="19">
         <v>8</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="O42" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P42" s="13">
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="O42" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P42" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="19">
         <v>8</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="G43" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="O43" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P43" s="13">
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="O43" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="19">
         <v>8</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="H44" s="14" t="s">
+      <c r="H44" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="K44" s="12" t="s">
+      <c r="K44" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="O44" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P44" s="13">
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="O44" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P44" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="19">
         <v>8</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="H45" s="14" t="s">
+      <c r="H45" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="I45" s="12" t="s">
+      <c r="I45" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="K45" s="12" t="s">
+      <c r="K45" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="O45" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P45" s="13">
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="O45" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P45" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="19">
         <v>9</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="O46" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P46" s="13">
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="O46" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="19">
         <v>9</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="H47" s="14" t="s">
+      <c r="H47" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="O47" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P47" s="13">
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="O47" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P47" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="19">
         <v>9</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H48" s="14" t="s">
+      <c r="H48" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I48" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="O48" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P48" s="13">
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="O48" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P48" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="19">
         <v>9</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H49" s="14" t="s">
+      <c r="H49" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="I49" s="12" t="s">
+      <c r="I49" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12"/>
-      <c r="O49" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P49" s="13">
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="O49" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P49" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="19">
         <v>9</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H50" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="I50" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L50" s="12"/>
-      <c r="M50" s="12"/>
-      <c r="O50" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P50" s="13">
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="O50" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P50" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="19">
         <v>10</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I51" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="O51" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P51" s="13">
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="O51" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P51" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="19">
         <v>10</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H52" s="14" t="s">
+      <c r="H52" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="I52" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="O52" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P52" s="13">
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="O52" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="19">
         <v>10</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="I53" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
-      <c r="O53" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P53" s="13">
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="O53" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P53" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="19">
         <v>11</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="I54" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="O54" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P54" s="13">
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="O54" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="19">
         <v>11</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="F55" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="H55" s="14" t="s">
+      <c r="H55" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="I55" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="O55" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P55" s="13">
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="O55" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P55" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="19">
         <v>11</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="I56" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="O56" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P56" s="13">
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="O56" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="19">
         <v>11</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H57" s="14" t="s">
+      <c r="H57" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="O57" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P57" s="13">
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="O57" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P57" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="19">
         <v>11</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="F58" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H58" s="14" t="s">
+      <c r="H58" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K58" s="12" t="s">
+      <c r="K58" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L58" s="12"/>
-      <c r="M58" s="12"/>
-      <c r="O58" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P58" s="13">
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="O58" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P58" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="19">
         <v>13</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="H59" s="14" t="s">
+      <c r="H59" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="I59" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L59" s="12"/>
-      <c r="M59" s="12"/>
-      <c r="O59" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P59" s="13">
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="O59" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="19">
         <v>13</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="H60" s="14" t="s">
+      <c r="H60" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="I60" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L60" s="12"/>
-      <c r="M60" s="12"/>
-      <c r="O60" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P60" s="13">
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="O60" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P60" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="19">
         <v>13</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H61" s="14" t="s">
+      <c r="H61" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="I61" s="12" t="s">
+      <c r="I61" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="O61" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P61" s="13">
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="O61" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="19">
         <v>17</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H62" s="14" t="s">
+      <c r="H62" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K62" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="O62" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P62" s="13">
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="O62" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="19">
         <v>17</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H63" s="14" t="s">
+      <c r="H63" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="I63" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="K63" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L63" s="12"/>
-      <c r="M63" s="12"/>
-      <c r="O63" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P63" s="13">
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="O63" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P63" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="19">
         <v>21</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H64" s="14" t="s">
+      <c r="H64" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="I64" s="12" t="s">
+      <c r="I64" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="K64" s="12" t="s">
+      <c r="K64" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L64" s="12"/>
-      <c r="M64" s="12"/>
-      <c r="O64" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P64" s="13">
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="O64" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P64" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="19">
         <v>21</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="G65" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H65" s="14" t="s">
+      <c r="H65" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="I65" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K65" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L65" s="12"/>
-      <c r="M65" s="12"/>
-      <c r="O65" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P65" s="13">
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="O65" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P65" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="19">
         <v>21</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="G66" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H66" s="14" t="s">
+      <c r="H66" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I66" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="K66" s="12" t="s">
+      <c r="K66" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="O66" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P66" s="13">
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="O66" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P66" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="19">
         <v>15</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H67" s="14" t="s">
+      <c r="H67" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="I67" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="O67" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P67" s="13">
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="O67" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P67" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="19">
         <v>19</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="12" t="s">
+      <c r="G68" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H68" s="14" t="s">
+      <c r="H68" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L68" s="12"/>
-      <c r="M68" s="12"/>
-      <c r="O68" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P68" s="13">
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="O68" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P68" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="19">
         <v>19</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G69" s="12" t="s">
+      <c r="G69" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H69" s="14" t="s">
+      <c r="H69" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="I69" s="12" t="s">
+      <c r="I69" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="O69" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P69" s="13">
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="O69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P69" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="19">
         <v>15</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="12" t="s">
+      <c r="G70" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H70" s="14" t="s">
+      <c r="H70" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I70" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L70" s="12"/>
-      <c r="M70" s="12"/>
-      <c r="O70" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P70" s="13">
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="O70" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P70" s="21">
         <v>46366</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="19">
         <v>24</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H71" s="14" t="s">
+      <c r="H71" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I71" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L71" s="12"/>
-      <c r="M71" s="12"/>
-      <c r="O71" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P71" s="13">
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="O71" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P71" s="21">
         <v>46366</v>
       </c>
     </row>
@@ -4659,6 +4691,163 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408A5FEF-2495-46B3-ABC4-715DC1824DA0}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="6" max="6" width="46.6328125" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13.08984375" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="10">
+        <v>46366</v>
+      </c>
+      <c r="I2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="10">
+        <v>46366</v>
+      </c>
+      <c r="I3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="10">
+        <v>46366</v>
+      </c>
+      <c r="I4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A87AFD-E38E-4752-8345-B70DBD79E2D9}">
   <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4747,133 +4936,133 @@
       </c>
     </row>
     <row r="2" spans="1:23" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="13">
+      <c r="C2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="14">
         <v>46336</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12" t="s">
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
     </row>
     <row r="3" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="13">
+      <c r="C3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="14">
         <v>46336</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12" t="s">
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEC8255-0EEE-4423-BFD7-EF6029BE1B7F}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4925,7 +5114,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>46336</v>
       </c>
       <c r="B2" s="6">
@@ -4963,7 +5152,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>46366</v>
       </c>
       <c r="B3" s="6">
@@ -5723,7 +5912,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>46033</v>
       </c>
       <c r="B23" s="6">
@@ -5761,7 +5950,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>46064</v>
       </c>
       <c r="B24" s="6">
@@ -5799,7 +5988,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>46092</v>
       </c>
       <c r="B25" s="6">
@@ -5837,7 +6026,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>46123</v>
       </c>
       <c r="B26" s="6">
@@ -5875,7 +6064,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>46153</v>
       </c>
       <c r="B27" s="6">
@@ -5913,7 +6102,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>46184</v>
       </c>
       <c r="B28" s="6">
@@ -5951,7 +6140,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>46214</v>
       </c>
       <c r="B29" s="6">
@@ -5989,7 +6178,7 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>46245</v>
       </c>
       <c r="B30" s="6">
@@ -6027,7 +6216,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="13">
+      <c r="A31" s="14">
         <v>46276</v>
       </c>
       <c r="B31" s="6">
@@ -6069,7 +6258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463636D4-2B56-4AA6-9F40-79E1FF7345CF}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6122,7 +6311,7 @@
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <f>IFERROR(C2/B2,0)</f>
         <v>0</v>
       </c>

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F82D7E-0F06-40DE-9209-9459C81AD6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE639A45-3A57-4FA8-9F2F-BADAE7AB66A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="4" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER_TC" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="477">
   <si>
     <t>TC ID</t>
   </si>
@@ -2157,7 +2157,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
@@ -2197,7 +2197,9 @@
         <v>93</v>
       </c>
       <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
+      <c r="R3" s="18" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
@@ -2415,7 +2417,7 @@
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
@@ -2455,7 +2457,9 @@
         <v>93</v>
       </c>
       <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
+      <c r="R10" s="18" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
@@ -3653,7 +3657,9 @@
         <v>93</v>
       </c>
       <c r="Q40" s="12"/>
-      <c r="R40" s="12"/>
+      <c r="R40" s="18" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE639A45-3A57-4FA8-9F2F-BADAE7AB66A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4E6B46-13B9-46B0-8E0C-040EE7429F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="476">
   <si>
     <t>TC ID</t>
   </si>
@@ -168,9 +168,6 @@
     <t>Duplikasi Asset Code</t>
   </si>
   <si>
-    <t>Endpoint tanpa auth</t>
-  </si>
-  <si>
     <t>Response time &lt; 2 detik</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
   </si>
   <si>
     <t>HTTP 409, error duplicate</t>
-  </si>
-  <si>
-    <t>HTTP 401 Unauthorized</t>
   </si>
   <si>
     <t>Response time &lt; 2000 ms</t>
@@ -1517,9 +1511,6 @@
     <t>Status: Open | Fixing | Testing | Closed</t>
   </si>
   <si>
-    <t>HTTP 200, total 16 aset tampil</t>
-  </si>
-  <si>
     <t>Test di Postman, backend jalan</t>
   </si>
   <si>
@@ -1592,13 +1583,20 @@
     <t>1. Buka Postman 
 2. GET /users/1 dengan Bearer token 3
 . Amati response</t>
+  </si>
+  <si>
+    <t>200 OK, 16 aset</t>
+  </si>
+  <si>
+    <t>Response time tercatat 
+di bawah 2000 ms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1617,6 +1615,18 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1664,7 +1674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1718,6 +1728,15 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2119,42 +2138,42 @@
       <c r="C2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
+      <c r="J2" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
       <c r="O2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P2" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q2" s="16"/>
       <c r="R2" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2164,41 +2183,41 @@
       <c r="B3" s="20">
         <v>8</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>456</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="21" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -2208,29 +2227,29 @@
       <c r="B4" s="20">
         <v>8</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="21"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="21" t="s">
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P4" s="19"/>
@@ -2244,29 +2263,29 @@
       <c r="B5" s="20">
         <v>8</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="21" t="s">
+      <c r="E5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="21" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P5" s="19"/>
@@ -2280,29 +2299,29 @@
       <c r="B6" s="20">
         <v>8</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="21" t="s">
+      <c r="E6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="21"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="21" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P6" s="19"/>
@@ -2316,29 +2335,29 @@
       <c r="B7" s="20">
         <v>9</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="21" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P7" s="19"/>
@@ -2352,29 +2371,29 @@
       <c r="B8" s="20">
         <v>9</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="21" t="s">
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P8" s="19"/>
@@ -2388,29 +2407,29 @@
       <c r="B9" s="20">
         <v>9</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="21" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P9" s="19"/>
@@ -2424,76 +2443,76 @@
       <c r="B10" s="20">
         <v>9</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="21" t="s">
+      <c r="E10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="21" t="s">
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="18" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="20">
         <v>9</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="19"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
     </row>
@@ -2508,18 +2527,18 @@
         <v>36</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>49</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="12"/>
@@ -2535,16 +2554,16 @@
     </row>
     <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B13" s="20">
         <v>13</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>20</v>
@@ -2553,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
@@ -2575,16 +2594,16 @@
     </row>
     <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B14" s="20">
         <v>13</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>20</v>
@@ -2593,13 +2612,13 @@
         <v>21</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -2615,16 +2634,16 @@
     </row>
     <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B15" s="20">
         <v>13</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>20</v>
@@ -2633,13 +2652,13 @@
         <v>21</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
@@ -2655,16 +2674,16 @@
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B16" s="20">
         <v>13</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
@@ -2673,13 +2692,13 @@
         <v>21</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -2695,16 +2714,16 @@
     </row>
     <row r="17" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B17" s="20">
         <v>13</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>20</v>
@@ -2713,13 +2732,13 @@
         <v>21</v>
       </c>
       <c r="G17" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>432</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>434</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
@@ -2735,16 +2754,16 @@
     </row>
     <row r="18" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18" s="20">
         <v>13</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>20</v>
@@ -2753,13 +2772,13 @@
         <v>21</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
@@ -2775,16 +2794,16 @@
     </row>
     <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="20">
         <v>13</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>20</v>
@@ -2793,13 +2812,13 @@
         <v>21</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
@@ -2815,16 +2834,16 @@
     </row>
     <row r="20" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B20" s="20">
         <v>13</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>20</v>
@@ -2833,13 +2852,13 @@
         <v>21</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
@@ -2855,16 +2874,16 @@
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B21" s="20">
         <v>13</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>20</v>
@@ -2873,13 +2892,13 @@
         <v>21</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -2895,16 +2914,16 @@
     </row>
     <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B22" s="20">
         <v>13</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>20</v>
@@ -2913,13 +2932,13 @@
         <v>21</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
@@ -2935,16 +2954,16 @@
     </row>
     <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B23" s="20">
         <v>13</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>20</v>
@@ -2953,13 +2972,13 @@
         <v>21</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
@@ -2975,31 +2994,31 @@
     </row>
     <row r="24" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B24" s="20">
         <v>13</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
@@ -3015,16 +3034,16 @@
     </row>
     <row r="25" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B25" s="20">
         <v>13</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>20</v>
@@ -3033,13 +3052,13 @@
         <v>21</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -3055,16 +3074,16 @@
     </row>
     <row r="26" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B26" s="20">
         <v>13</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>20</v>
@@ -3073,13 +3092,13 @@
         <v>21</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -3095,31 +3114,31 @@
     </row>
     <row r="27" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B27" s="20">
         <v>13</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -3135,31 +3154,31 @@
     </row>
     <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B28" s="20">
         <v>27</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
@@ -3175,31 +3194,31 @@
     </row>
     <row r="29" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B29" s="20">
         <v>27</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
@@ -3215,31 +3234,31 @@
     </row>
     <row r="30" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B30" s="20">
         <v>27</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
@@ -3255,31 +3274,31 @@
     </row>
     <row r="31" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B31" s="20">
         <v>27</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
@@ -3295,31 +3314,31 @@
     </row>
     <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B32" s="20">
         <v>27</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -3335,31 +3354,31 @@
     </row>
     <row r="33" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B33" s="20">
         <v>27</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -3375,31 +3394,31 @@
     </row>
     <row r="34" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B34" s="20">
         <v>27</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -3415,16 +3434,16 @@
     </row>
     <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B35" s="20">
         <v>27</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>20</v>
@@ -3433,13 +3452,13 @@
         <v>21</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -3455,16 +3474,16 @@
     </row>
     <row r="36" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B36" s="20">
         <v>27</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>20</v>
@@ -3473,13 +3492,13 @@
         <v>21</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
@@ -3495,31 +3514,31 @@
     </row>
     <row r="37" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B37" s="20">
         <v>27</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -3535,31 +3554,31 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B38" s="20">
         <v>27</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
@@ -3575,31 +3594,31 @@
     </row>
     <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B39" s="20">
         <v>27</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -3615,16 +3634,16 @@
     </row>
     <row r="40" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B40" s="20">
         <v>8</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>20</v>
@@ -3633,19 +3652,19 @@
         <v>21</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
@@ -3654,40 +3673,40 @@
         <v>25</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q40" s="12"/>
       <c r="R40" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B41" s="20">
         <v>8</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
@@ -3703,31 +3722,31 @@
     </row>
     <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B42" s="20">
         <v>8</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
@@ -3743,16 +3762,16 @@
     </row>
     <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B43" s="20">
         <v>8</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>20</v>
@@ -3761,13 +3780,13 @@
         <v>21</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
@@ -3783,31 +3802,31 @@
     </row>
     <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B44" s="20">
         <v>8</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
@@ -3823,37 +3842,37 @@
     </row>
     <row r="45" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B45" s="20">
         <v>8</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
@@ -3862,23 +3881,23 @@
         <v>25</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q45" s="12"/>
       <c r="R45" s="12"/>
     </row>
     <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B46" s="20">
         <v>9</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>20</v>
@@ -3887,19 +3906,19 @@
         <v>21</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
@@ -3908,38 +3927,38 @@
         <v>25</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
     </row>
     <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B47" s="20">
         <v>9</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -3955,16 +3974,16 @@
     </row>
     <row r="48" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B48" s="20">
         <v>9</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>20</v>
@@ -3973,13 +3992,13 @@
         <v>21</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
@@ -3995,31 +4014,31 @@
     </row>
     <row r="49" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B49" s="20">
         <v>9</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
@@ -4035,31 +4054,31 @@
     </row>
     <row r="50" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B50" s="20">
         <v>9</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
@@ -4075,16 +4094,16 @@
     </row>
     <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B51" s="20">
         <v>10</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>20</v>
@@ -4093,13 +4112,13 @@
         <v>21</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
@@ -4115,31 +4134,31 @@
     </row>
     <row r="52" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" s="20">
         <v>10</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
@@ -4155,31 +4174,31 @@
     </row>
     <row r="53" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B53" s="20">
         <v>10</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
@@ -4195,16 +4214,16 @@
     </row>
     <row r="54" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B54" s="20">
         <v>11</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>20</v>
@@ -4213,13 +4232,13 @@
         <v>21</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
@@ -4235,16 +4254,16 @@
     </row>
     <row r="55" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B55" s="20">
         <v>11</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>20</v>
@@ -4253,13 +4272,13 @@
         <v>21</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
@@ -4275,16 +4294,16 @@
     </row>
     <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B56" s="20">
         <v>11</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>20</v>
@@ -4293,13 +4312,13 @@
         <v>21</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
@@ -4315,16 +4334,16 @@
     </row>
     <row r="57" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B57" s="20">
         <v>11</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>20</v>
@@ -4333,13 +4352,13 @@
         <v>21</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
@@ -4355,16 +4374,16 @@
     </row>
     <row r="58" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B58" s="20">
         <v>11</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>20</v>
@@ -4373,13 +4392,13 @@
         <v>21</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
@@ -4395,16 +4414,16 @@
     </row>
     <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B59" s="20">
         <v>13</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>20</v>
@@ -4413,13 +4432,13 @@
         <v>21</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
@@ -4435,31 +4454,31 @@
     </row>
     <row r="60" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B60" s="20">
         <v>13</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
@@ -4475,31 +4494,31 @@
     </row>
     <row r="61" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B61" s="20">
         <v>13</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
@@ -4515,31 +4534,31 @@
     </row>
     <row r="62" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B62" s="20">
         <v>17</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
@@ -4555,31 +4574,31 @@
     </row>
     <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" s="20">
         <v>17</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
@@ -4595,16 +4614,16 @@
     </row>
     <row r="64" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B64" s="20">
         <v>21</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>20</v>
@@ -4613,13 +4632,13 @@
         <v>21</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
@@ -4635,31 +4654,31 @@
     </row>
     <row r="65" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B65" s="20">
         <v>21</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
@@ -4675,31 +4694,31 @@
     </row>
     <row r="66" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B66" s="20">
         <v>21</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J66" s="9"/>
       <c r="K66" s="9"/>
@@ -4715,16 +4734,16 @@
     </row>
     <row r="67" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B67" s="20">
         <v>15</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>20</v>
@@ -4733,13 +4752,13 @@
         <v>21</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
@@ -4755,16 +4774,16 @@
     </row>
     <row r="68" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B68" s="20">
         <v>19</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>20</v>
@@ -4773,13 +4792,13 @@
         <v>21</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
@@ -4795,31 +4814,31 @@
     </row>
     <row r="69" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B69" s="20">
         <v>19</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J69" s="9"/>
       <c r="K69" s="9"/>
@@ -4835,16 +4854,16 @@
     </row>
     <row r="70" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B70" s="20">
         <v>15</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>20</v>
@@ -4853,13 +4872,13 @@
         <v>21</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
@@ -4875,31 +4894,31 @@
     </row>
     <row r="71" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B71" s="20">
         <v>24</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
@@ -4914,6 +4933,7 @@
       <c r="R71" s="12"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4940,28 +4960,28 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>451</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -4971,28 +4991,28 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -5002,28 +5022,28 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="H3" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -5059,12 +5079,12 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -5102,16 +5122,16 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>2</v>
@@ -5120,16 +5140,16 @@
         <v>11</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>8</v>
@@ -5138,10 +5158,10 @@
         <v>9</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O1" s="13" t="s">
         <v>13</v>
@@ -5150,129 +5170,129 @@
         <v>10</v>
       </c>
       <c r="Q1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="15" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>469</v>
-      </c>
       <c r="P2" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="12"/>
       <c r="T2" s="15" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="W2" s="4"/>
     </row>
     <row r="3" spans="1:23" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="15" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R3" s="9"/>
       <c r="S3" s="12"/>
       <c r="T3" s="15" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="W3" s="4"/>
     </row>
@@ -5296,40 +5316,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>17</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -5340,45 +5360,45 @@
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="17">
+        <v>0</v>
+      </c>
+      <c r="E2" s="17">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17">
+        <v>0</v>
+      </c>
+      <c r="G2" s="17">
+        <v>0</v>
+      </c>
+      <c r="H2" s="17">
+        <v>0</v>
+      </c>
+      <c r="I2" s="17">
+        <v>0</v>
+      </c>
+      <c r="J2" s="17">
+        <v>0</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="D2" s="17">
-        <v>0</v>
-      </c>
-      <c r="E2" s="17">
-        <v>0</v>
-      </c>
-      <c r="F2" s="17">
-        <v>0</v>
-      </c>
-      <c r="G2" s="17">
-        <v>0</v>
-      </c>
-      <c r="H2" s="17">
-        <v>0</v>
-      </c>
-      <c r="I2" s="17">
-        <v>0</v>
-      </c>
-      <c r="J2" s="17">
-        <v>0</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="17">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="17">
         <v>0</v>
@@ -5402,21 +5422,21 @@
         <v>0</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" s="17">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" s="17">
         <v>0</v>
@@ -5440,21 +5460,21 @@
         <v>0</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="17">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" s="17">
         <v>0</v>
@@ -5478,21 +5498,21 @@
         <v>0</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="17">
         <v>5</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" s="17">
         <v>0</v>
@@ -5516,21 +5536,21 @@
         <v>0</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B7" s="17">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D7" s="17">
         <v>5</v>
@@ -5554,21 +5574,21 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="17">
         <v>7</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" s="17">
         <v>3</v>
@@ -5592,21 +5612,21 @@
         <v>0</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="17">
         <v>8</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D9" s="17">
         <v>5</v>
@@ -5630,21 +5650,21 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B10" s="17">
         <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="17">
         <v>5</v>
@@ -5668,21 +5688,21 @@
         <v>1</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B11" s="17">
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" s="17">
         <v>4</v>
@@ -5706,21 +5726,21 @@
         <v>0</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" s="17">
         <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D12" s="17">
         <v>6</v>
@@ -5744,21 +5764,21 @@
         <v>0</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B13" s="17">
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" s="17">
         <v>4</v>
@@ -5782,21 +5802,21 @@
         <v>0</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14" s="17">
         <v>13</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14" s="17">
         <v>5</v>
@@ -5820,21 +5840,21 @@
         <v>0</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B15" s="17">
         <v>14</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D15" s="17">
         <v>5</v>
@@ -5858,21 +5878,21 @@
         <v>0</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" s="17">
         <v>15</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" s="17">
         <v>5</v>
@@ -5896,21 +5916,21 @@
         <v>0</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B17" s="17">
         <v>16</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" s="17">
         <v>5</v>
@@ -5934,21 +5954,21 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="17">
         <v>17</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D18" s="17">
         <v>4</v>
@@ -5972,21 +5992,21 @@
         <v>0</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="17">
         <v>18</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" s="17">
         <v>4</v>
@@ -6010,21 +6030,21 @@
         <v>0</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B20" s="17">
         <v>19</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" s="17">
         <v>4</v>
@@ -6048,21 +6068,21 @@
         <v>0</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" s="17">
         <v>20</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D21" s="17">
         <v>6</v>
@@ -6086,10 +6106,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -6100,7 +6120,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D22" s="17">
         <v>4</v>
@@ -6124,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
@@ -6138,7 +6158,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D23" s="17">
         <v>4</v>
@@ -6162,10 +6182,10 @@
         <v>0</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
@@ -6176,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D24" s="17">
         <v>4</v>
@@ -6200,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -6214,7 +6234,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D25" s="17">
         <v>5</v>
@@ -6238,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
@@ -6252,7 +6272,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D26" s="17">
         <v>4</v>
@@ -6276,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
@@ -6290,7 +6310,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" s="17">
         <v>9</v>
@@ -6314,10 +6334,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -6328,7 +6348,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" s="17">
         <v>6</v>
@@ -6352,10 +6372,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -6366,7 +6386,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="17">
         <v>4</v>
@@ -6390,10 +6410,10 @@
         <v>0</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
@@ -6404,7 +6424,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D30" s="17">
         <v>5</v>
@@ -6428,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
@@ -6442,7 +6462,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D31" s="17">
         <v>6</v>
@@ -6466,10 +6486,10 @@
         <v>0</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6495,19 +6515,19 @@
         <v>2</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="F1" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -6520,7 +6540,7 @@
       </c>
       <c r="C2" s="17">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"PASS")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="17">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"FAIL")</f>
@@ -6532,12 +6552,12 @@
       </c>
       <c r="F2" s="23">
         <f>IFERROR(C2/B2,0)</f>
-        <v>0.27272727272727271</v>
+        <v>0.36363636363636365</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B3" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A3)</f>
@@ -6562,7 +6582,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B4" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A4)</f>
@@ -6587,7 +6607,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B5" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A5)</f>
@@ -6612,7 +6632,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B6" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A6)</f>
@@ -6637,7 +6657,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B7" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A7)</f>
@@ -6662,7 +6682,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B8" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A8)</f>
@@ -6687,7 +6707,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B9" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A9)</f>
@@ -6712,7 +6732,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A10)</f>
@@ -6737,7 +6757,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B11" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A11)</f>
@@ -6762,7 +6782,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B12" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A12)</f>
@@ -6787,7 +6807,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B13" s="17">
         <f>COUNTIF(MASTER_TC!C:C,A13)</f>

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4E6B46-13B9-46B0-8E0C-040EE7429F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46B730B-B48E-4090-B2D0-1E521B6A5101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="481">
   <si>
     <t>TC ID</t>
   </si>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>Assets</t>
-  </si>
-  <si>
-    <t>Bearer token, aset terdaftar</t>
   </si>
   <si>
     <t>TC-ASSET-002</t>
@@ -1590,6 +1587,29 @@
   <si>
     <t>Response time tercatat 
 di bawah 2000 ms</t>
+  </si>
+  <si>
+    <t>Test response time di 
+Postman</t>
+  </si>
+  <si>
+    <t>1. Buka Postman 
+2. Kirim GET /api/assets 
+3. Catat response time</t>
+  </si>
+  <si>
+    <t>Postman siap, backend 
+jalan, token valid</t>
+  </si>
+  <si>
+    <t>Bearer token, aset
+ terdaftar</t>
+  </si>
+  <si>
+    <t>Test tanpa token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401 Unauthorized </t>
   </si>
 </sst>
 </file>
@@ -2157,7 +2177,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>79</v>
@@ -2173,7 +2193,7 @@
       </c>
       <c r="Q2" s="16"/>
       <c r="R2" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2201,7 +2221,7 @@
         <v>49</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>79</v>
@@ -2217,7 +2237,7 @@
       </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -2461,7 +2481,7 @@
         <v>55</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>79</v>
@@ -2477,10 +2497,10 @@
       </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="18" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>34</v>
       </c>
@@ -2493,15 +2513,23 @@
       <c r="D11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="18"/>
+      <c r="E11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>476</v>
+      </c>
       <c r="I11" s="9" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>79</v>
@@ -2509,12 +2537,16 @@
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
-      <c r="O11" s="9"/>
+      <c r="O11" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="P11" s="19" t="s">
         <v>91</v>
       </c>
       <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
+      <c r="R11" s="15" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
@@ -2540,8 +2572,12 @@
       <c r="I12" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="12"/>
+      <c r="J12" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -2550,7 +2586,9 @@
       </c>
       <c r="P12" s="19"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
+      <c r="R12" s="12" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
@@ -2563,7 +2601,7 @@
         <v>178</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>20</v>
@@ -2571,14 +2609,14 @@
       <c r="F13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>179</v>
+      <c r="G13" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
@@ -2594,7 +2632,7 @@
     </row>
     <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="20">
         <v>13</v>
@@ -2603,7 +2641,7 @@
         <v>178</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>20</v>
@@ -2612,13 +2650,13 @@
         <v>21</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -2634,7 +2672,7 @@
     </row>
     <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B15" s="20">
         <v>13</v>
@@ -2643,7 +2681,7 @@
         <v>178</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>20</v>
@@ -2652,13 +2690,13 @@
         <v>21</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
@@ -2674,7 +2712,7 @@
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="20">
         <v>13</v>
@@ -2683,7 +2721,7 @@
         <v>178</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
@@ -2692,13 +2730,13 @@
         <v>21</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -2714,7 +2752,7 @@
     </row>
     <row r="17" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="20">
         <v>13</v>
@@ -2723,7 +2761,7 @@
         <v>178</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>20</v>
@@ -2732,13 +2770,13 @@
         <v>21</v>
       </c>
       <c r="G17" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="I17" s="11" t="s">
         <v>431</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>432</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
@@ -2754,7 +2792,7 @@
     </row>
     <row r="18" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="20">
         <v>13</v>
@@ -2763,7 +2801,7 @@
         <v>178</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>20</v>
@@ -2772,13 +2810,13 @@
         <v>21</v>
       </c>
       <c r="G18" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="H18" s="15" t="s">
-        <v>436</v>
-      </c>
       <c r="I18" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
@@ -2794,7 +2832,7 @@
     </row>
     <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" s="20">
         <v>13</v>
@@ -2803,7 +2841,7 @@
         <v>178</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>20</v>
@@ -2812,13 +2850,13 @@
         <v>21</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
@@ -2834,7 +2872,7 @@
     </row>
     <row r="20" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B20" s="20">
         <v>13</v>
@@ -2843,7 +2881,7 @@
         <v>178</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>20</v>
@@ -2852,13 +2890,13 @@
         <v>21</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
@@ -2874,7 +2912,7 @@
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B21" s="20">
         <v>13</v>
@@ -2883,7 +2921,7 @@
         <v>178</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>20</v>
@@ -2892,13 +2930,13 @@
         <v>21</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -2914,7 +2952,7 @@
     </row>
     <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B22" s="20">
         <v>13</v>
@@ -2923,7 +2961,7 @@
         <v>178</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>20</v>
@@ -2932,13 +2970,13 @@
         <v>21</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
@@ -2954,7 +2992,7 @@
     </row>
     <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B23" s="20">
         <v>13</v>
@@ -2963,7 +3001,7 @@
         <v>178</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>20</v>
@@ -2972,13 +3010,13 @@
         <v>21</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
@@ -2994,7 +3032,7 @@
     </row>
     <row r="24" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B24" s="20">
         <v>13</v>
@@ -3003,7 +3041,7 @@
         <v>178</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>20</v>
@@ -3012,13 +3050,13 @@
         <v>48</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
@@ -3034,7 +3072,7 @@
     </row>
     <row r="25" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B25" s="20">
         <v>13</v>
@@ -3043,7 +3081,7 @@
         <v>178</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>20</v>
@@ -3052,13 +3090,13 @@
         <v>21</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -3074,7 +3112,7 @@
     </row>
     <row r="26" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" s="20">
         <v>13</v>
@@ -3083,7 +3121,7 @@
         <v>178</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>20</v>
@@ -3092,13 +3130,13 @@
         <v>21</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -3114,7 +3152,7 @@
     </row>
     <row r="27" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B27" s="20">
         <v>13</v>
@@ -3123,7 +3161,7 @@
         <v>178</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>20</v>
@@ -3132,13 +3170,13 @@
         <v>48</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -3154,31 +3192,31 @@
     </row>
     <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B28" s="20">
         <v>27</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
@@ -3194,31 +3232,31 @@
     </row>
     <row r="29" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B29" s="20">
         <v>27</v>
       </c>
       <c r="C29" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
@@ -3234,31 +3272,31 @@
     </row>
     <row r="30" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" s="20">
         <v>27</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="I30" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
@@ -3274,31 +3312,31 @@
     </row>
     <row r="31" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="20">
         <v>27</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
@@ -3314,31 +3352,31 @@
     </row>
     <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B32" s="20">
         <v>27</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -3354,31 +3392,31 @@
     </row>
     <row r="33" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B33" s="20">
         <v>27</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -3394,31 +3432,31 @@
     </row>
     <row r="34" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B34" s="20">
         <v>27</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -3434,16 +3472,16 @@
     </row>
     <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B35" s="20">
         <v>27</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>20</v>
@@ -3452,13 +3490,13 @@
         <v>21</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -3474,16 +3512,16 @@
     </row>
     <row r="36" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B36" s="20">
         <v>27</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>20</v>
@@ -3492,13 +3530,13 @@
         <v>21</v>
       </c>
       <c r="G36" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
@@ -3514,31 +3552,31 @@
     </row>
     <row r="37" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" s="20">
         <v>27</v>
       </c>
       <c r="C37" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -3554,31 +3592,31 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B38" s="20">
         <v>27</v>
       </c>
       <c r="C38" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H38" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
@@ -3594,31 +3632,31 @@
     </row>
     <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B39" s="20">
         <v>27</v>
       </c>
       <c r="C39" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -3634,16 +3672,16 @@
     </row>
     <row r="40" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B40" s="20">
         <v>8</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>20</v>
@@ -3652,16 +3690,16 @@
         <v>21</v>
       </c>
       <c r="G40" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>280</v>
-      </c>
       <c r="J40" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>79</v>
@@ -3677,21 +3715,21 @@
       </c>
       <c r="Q40" s="12"/>
       <c r="R40" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B41" s="20">
         <v>8</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>46</v>
@@ -3700,13 +3738,13 @@
         <v>21</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
@@ -3722,16 +3760,16 @@
     </row>
     <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B42" s="20">
         <v>8</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>46</v>
@@ -3740,13 +3778,13 @@
         <v>21</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
@@ -3762,16 +3800,16 @@
     </row>
     <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B43" s="20">
         <v>8</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>20</v>
@@ -3780,13 +3818,13 @@
         <v>21</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>289</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
@@ -3802,16 +3840,16 @@
     </row>
     <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B44" s="20">
         <v>8</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>46</v>
@@ -3820,13 +3858,13 @@
         <v>21</v>
       </c>
       <c r="G44" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="I44" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>294</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
@@ -3842,16 +3880,16 @@
     </row>
     <row r="45" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B45" s="20">
         <v>8</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>20</v>
@@ -3860,16 +3898,16 @@
         <v>48</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>80</v>
@@ -3888,16 +3926,16 @@
     </row>
     <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B46" s="20">
         <v>9</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>299</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>300</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>20</v>
@@ -3906,16 +3944,16 @@
         <v>21</v>
       </c>
       <c r="G46" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="I46" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="H46" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>302</v>
-      </c>
       <c r="J46" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>80</v>
@@ -3934,16 +3972,16 @@
     </row>
     <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B47" s="20">
         <v>9</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>46</v>
@@ -3952,13 +3990,13 @@
         <v>21</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="I47" s="9" t="s">
         <v>305</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>306</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -3974,16 +4012,16 @@
     </row>
     <row r="48" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B48" s="20">
         <v>9</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>20</v>
@@ -3992,13 +4030,13 @@
         <v>21</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
@@ -4014,16 +4052,16 @@
     </row>
     <row r="49" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B49" s="20">
         <v>9</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>46</v>
@@ -4032,13 +4070,13 @@
         <v>21</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
@@ -4054,16 +4092,16 @@
     </row>
     <row r="50" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B50" s="20">
         <v>9</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>46</v>
@@ -4072,13 +4110,13 @@
         <v>21</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
@@ -4094,16 +4132,16 @@
     </row>
     <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B51" s="20">
         <v>10</v>
       </c>
       <c r="C51" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>20</v>
@@ -4112,13 +4150,13 @@
         <v>21</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
@@ -4134,16 +4172,16 @@
     </row>
     <row r="52" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B52" s="20">
         <v>10</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>20</v>
@@ -4152,13 +4190,13 @@
         <v>48</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
@@ -4174,16 +4212,16 @@
     </row>
     <row r="53" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B53" s="20">
         <v>10</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>46</v>
@@ -4192,13 +4230,13 @@
         <v>48</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
@@ -4214,7 +4252,7 @@
     </row>
     <row r="54" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B54" s="20">
         <v>11</v>
@@ -4223,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>20</v>
@@ -4232,13 +4270,13 @@
         <v>21</v>
       </c>
       <c r="G54" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="I54" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>328</v>
       </c>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
@@ -4254,7 +4292,7 @@
     </row>
     <row r="55" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B55" s="20">
         <v>11</v>
@@ -4263,7 +4301,7 @@
         <v>70</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>20</v>
@@ -4272,13 +4310,13 @@
         <v>21</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="I55" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>328</v>
       </c>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
@@ -4294,7 +4332,7 @@
     </row>
     <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B56" s="20">
         <v>11</v>
@@ -4303,7 +4341,7 @@
         <v>70</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>20</v>
@@ -4312,13 +4350,13 @@
         <v>21</v>
       </c>
       <c r="G56" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="I56" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>328</v>
       </c>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
@@ -4334,7 +4372,7 @@
     </row>
     <row r="57" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B57" s="20">
         <v>11</v>
@@ -4343,7 +4381,7 @@
         <v>70</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>20</v>
@@ -4352,13 +4390,13 @@
         <v>21</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
@@ -4374,7 +4412,7 @@
     </row>
     <row r="58" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B58" s="20">
         <v>11</v>
@@ -4383,7 +4421,7 @@
         <v>70</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>20</v>
@@ -4392,13 +4430,13 @@
         <v>21</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
@@ -4414,16 +4452,16 @@
     </row>
     <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B59" s="20">
         <v>13</v>
       </c>
       <c r="C59" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>20</v>
@@ -4432,13 +4470,13 @@
         <v>21</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="I59" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>416</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>343</v>
       </c>
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
@@ -4454,16 +4492,16 @@
     </row>
     <row r="60" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B60" s="20">
         <v>13</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>46</v>
@@ -4472,13 +4510,13 @@
         <v>21</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
@@ -4494,16 +4532,16 @@
     </row>
     <row r="61" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B61" s="20">
         <v>13</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>20</v>
@@ -4512,13 +4550,13 @@
         <v>48</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
@@ -4534,16 +4572,16 @@
     </row>
     <row r="62" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B62" s="20">
         <v>17</v>
       </c>
       <c r="C62" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>20</v>
@@ -4552,13 +4590,13 @@
         <v>48</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
@@ -4574,16 +4612,16 @@
     </row>
     <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B63" s="20">
         <v>17</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>20</v>
@@ -4592,13 +4630,13 @@
         <v>48</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
@@ -4614,16 +4652,16 @@
     </row>
     <row r="64" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B64" s="20">
         <v>21</v>
       </c>
       <c r="C64" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>358</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>359</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>20</v>
@@ -4632,13 +4670,13 @@
         <v>21</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
@@ -4654,16 +4692,16 @@
     </row>
     <row r="65" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B65" s="20">
         <v>21</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>20</v>
@@ -4672,13 +4710,13 @@
         <v>48</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
@@ -4694,16 +4732,16 @@
     </row>
     <row r="66" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B66" s="20">
         <v>21</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>20</v>
@@ -4712,13 +4750,13 @@
         <v>48</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J66" s="9"/>
       <c r="K66" s="9"/>
@@ -4734,7 +4772,7 @@
     </row>
     <row r="67" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B67" s="20">
         <v>15</v>
@@ -4743,7 +4781,7 @@
         <v>172</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>20</v>
@@ -4752,13 +4790,13 @@
         <v>21</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
@@ -4774,7 +4812,7 @@
     </row>
     <row r="68" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B68" s="20">
         <v>19</v>
@@ -4783,7 +4821,7 @@
         <v>172</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>20</v>
@@ -4792,13 +4830,13 @@
         <v>21</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
@@ -4814,7 +4852,7 @@
     </row>
     <row r="69" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B69" s="20">
         <v>19</v>
@@ -4823,7 +4861,7 @@
         <v>172</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>20</v>
@@ -4832,13 +4870,13 @@
         <v>48</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J69" s="9"/>
       <c r="K69" s="9"/>
@@ -4854,7 +4892,7 @@
     </row>
     <row r="70" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B70" s="20">
         <v>15</v>
@@ -4863,7 +4901,7 @@
         <v>172</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>20</v>
@@ -4872,13 +4910,13 @@
         <v>21</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
@@ -4894,7 +4932,7 @@
     </row>
     <row r="71" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B71" s="20">
         <v>24</v>
@@ -4903,7 +4941,7 @@
         <v>172</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>20</v>
@@ -4912,13 +4950,13 @@
         <v>48</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
@@ -4960,28 +4998,28 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>448</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>449</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -4997,16 +5035,16 @@
         <v>91</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>75</v>
@@ -5028,13 +5066,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>460</v>
-      </c>
       <c r="E3" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -5079,12 +5117,12 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -5122,7 +5160,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>57</v>
@@ -5187,7 +5225,7 @@
         <v>69</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>25</v>
@@ -5196,35 +5234,35 @@
         <v>91</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>463</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>464</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>71</v>
       </c>
       <c r="N2" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>465</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>466</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>72</v>
@@ -5235,7 +5273,7 @@
       <c r="R2" s="9"/>
       <c r="S2" s="12"/>
       <c r="T2" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W2" s="4"/>
     </row>
@@ -5244,7 +5282,7 @@
         <v>73</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>25</v>
@@ -5253,7 +5291,7 @@
         <v>91</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -5262,26 +5300,26 @@
         <v>21</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M3" s="9" t="s">
         <v>71</v>
       </c>
       <c r="N3" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>468</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>469</v>
       </c>
       <c r="P3" s="9" t="s">
         <v>72</v>
@@ -5292,7 +5330,7 @@
       <c r="R3" s="9"/>
       <c r="S3" s="12"/>
       <c r="T3" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="W3" s="4"/>
     </row>
@@ -6540,7 +6578,7 @@
       </c>
       <c r="C2" s="17">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"PASS")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="17">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"FAIL")</f>
@@ -6552,7 +6590,7 @@
       </c>
       <c r="F2" s="23">
         <f>IFERROR(C2/B2,0)</f>
-        <v>0.36363636363636365</v>
+        <v>0.45454545454545453</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24792B35-A59E-4F43-B18D-85AD95C0D9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CE23D1-E662-4731-B5AE-DA8EEE87D99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="220" windowWidth="14400" windowHeight="7810" activeTab="1" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
+    <workbookView xWindow="-90" yWindow="220" windowWidth="14400" windowHeight="7810" firstSheet="3" activeTab="4" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER_TC" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="483">
   <si>
     <t>TC ID</t>
   </si>
@@ -1613,6 +1613,9 @@
   </si>
   <si>
     <t>POST /auth/change-password 404 Endpoint tidak ditemukan</t>
+  </si>
+  <si>
+    <t>Retest 14/10 — masih 500. Backend crash</t>
   </si>
 </sst>
 </file>
@@ -5074,7 +5077,7 @@
         <v>91</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>298</v>

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\docs\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C72B03-4FD8-4DB9-B67A-325E08392D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8BEB4B-BC8F-42A0-BC05-0F46C7155260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="220" windowWidth="14400" windowHeight="7810" firstSheet="2" activeTab="2" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
+    <workbookView xWindow="0" yWindow="220" windowWidth="14400" windowHeight="7810" xr2:uid="{D20540B9-5A4B-4C0F-A1AA-6997D01BA992}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER_TC" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="500">
   <si>
     <t>TC ID</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>P1</t>
-  </si>
-  <si>
-    <t>Backend jalan, Postman siap</t>
   </si>
   <si>
     <t xml:space="preserve">1. Buka Postman
@@ -247,9 +244,6 @@
   </si>
   <si>
     <t>Selalu</t>
-  </si>
-  <si>
-    <t>Open</t>
   </si>
   <si>
     <t>BUG-002</t>
@@ -1024,16 +1018,7 @@
     <t>DELETE user sebagai admin (403)</t>
   </si>
   <si>
-    <t>TC-LOC-001</t>
-  </si>
-  <si>
     <t>Locations</t>
-  </si>
-  <si>
-    <t>GET list lokasi</t>
-  </si>
-  <si>
-    <t>200, 2 lokasi (HO, Marketing)</t>
   </si>
   <si>
     <t>TC-LOC-002</t>
@@ -1337,10 +1322,6 @@
 2. Amati</t>
   </si>
   <si>
-    <t>1. GET /locations 
-2. Amati</t>
-  </si>
-  <si>
     <t>1. POST /locations 
 2. Body valid 
 3. Amati</t>
@@ -1518,13 +1499,7 @@
 diimplementasi</t>
   </si>
   <si>
-    <t>500 Internal Server Error</t>
-  </si>
-  <si>
     <t>Dev</t>
-  </si>
-  <si>
-    <t>404 Endpoint tidak ditemukan</t>
   </si>
   <si>
     <t>Test response time di 
@@ -1559,9 +1534,6 @@
     <t>BUG-003</t>
   </si>
   <si>
-    <t>200 OK, list aset tampil (16 aset)</t>
-  </si>
-  <si>
     <t>200 OK, detail aset tampil</t>
   </si>
   <si>
@@ -1589,57 +1561,25 @@
     <t>GET /users/1 500 Internal Server Error</t>
   </si>
   <si>
-    <t>GET /auth/me 500 — Unknown column 'created_at' in field list</t>
-  </si>
-  <si>
     <t>POST /auth/change-password 404</t>
   </si>
   <si>
+    <t>1. POST /auth/change-password 2. Body old+new 3. Amati response</t>
+  </si>
+  <si>
     <t>200 OK</t>
   </si>
   <si>
-    <t>User tidak bisa ganti password</t>
-  </si>
-  <si>
     <t>screenshots/BUG-001.png</t>
   </si>
   <si>
-    <t>200 OK, detail user</t>
-  </si>
-  <si>
-    <t>Detail user tidak bisa diakses</t>
-  </si>
-  <si>
     <t>screenshots/BUG-002.png</t>
   </si>
   <si>
-    <t>Belum di-fix</t>
-  </si>
-  <si>
-    <t>200 OK, data user</t>
-  </si>
-  <si>
     <t>User tidak bisa akses profil</t>
   </si>
   <si>
     <t>screenshots/BUG-003.png</t>
-  </si>
-  <si>
-    <t>BUG baru — root cause 
-sama BUG-002</t>
-  </si>
-  <si>
-    <t>Fixed &amp; verified 
-14/10/2026</t>
-  </si>
-  <si>
-    <t>GET /auth/me 500 
-Unknown column created_at</t>
-  </si>
-  <si>
-    <t>1. POST /auth/change-password 
-2. Body old+new 
-3. Amati response</t>
   </si>
   <si>
     <t>1. GET /users/1 
@@ -1650,13 +1590,93 @@
     <t>1. GET /auth/me 
 2. Bearer token 
 3. Amati response</t>
+  </si>
+  <si>
+    <t>BUG-004</t>
+  </si>
+  <si>
+    <t>GET /auth/me 500 — Unknown column 'created_at'</t>
+  </si>
+  <si>
+    <t>GET /users 500 — Unknown column 'created_at'</t>
+  </si>
+  <si>
+    <t>Fixed &amp; verified</t>
+  </si>
+  <si>
+    <t>GET /users/1 500</t>
+  </si>
+  <si>
+    <t>Fixed setelah created_at ditambah</t>
+  </si>
+  <si>
+    <t>GET /auth/me 500 created_at</t>
+  </si>
+  <si>
+    <t>GET /users 500 created_at</t>
+  </si>
+  <si>
+    <t>List user tidak bisa diakses</t>
+  </si>
+  <si>
+    <t>screenshots/BUG-004.png</t>
+  </si>
+  <si>
+    <t>1. GET /users 
+2. Bearer token 
+3. Amati response</t>
+  </si>
+  <si>
+    <t>Fixed setelah created_at 
+ditambah</t>
+  </si>
+  <si>
+    <t>User tidak bisa ganti 
+password</t>
+  </si>
+  <si>
+    <t>Detail user tidak bisa 
+diakses</t>
+  </si>
+  <si>
+    <t>TC-USER-006</t>
+  </si>
+  <si>
+    <t>GET /users/1 Detail User</t>
+  </si>
+  <si>
+    <t>200 OK, detail user ID 1</t>
+  </si>
+  <si>
+    <t>200 OK, detail user tampil</t>
+  </si>
+  <si>
+    <t>Retest setelah fix created_at</t>
+  </si>
+  <si>
+    <t>Bearer token, user ID 1 
+ada</t>
+  </si>
+  <si>
+    <t>Aset bertambah dari 16 menjadi 17, sistem normal</t>
+  </si>
+  <si>
+    <t>200 OK, data 17 aset tampil 
+di database</t>
+  </si>
+  <si>
+    <t>Backend jalan, Postman 
+siap</t>
+  </si>
+  <si>
+    <t>anji</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1687,6 +1707,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1747,7 +1773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1767,7 +1793,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1795,16 +1820,32 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2199,12 +2240,12 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12" t="s">
-        <v>36</v>
+      <c r="B2" s="12"/>
+      <c r="C2" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>19</v>
@@ -2215,49 +2256,49 @@
       <c r="F2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="14" t="s">
-        <v>451</v>
+      <c r="J2" s="26" t="s">
+        <v>497</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="25" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="16">
+        <v>25</v>
+      </c>
+      <c r="B3" s="15">
         <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>20</v>
@@ -2268,42 +2309,42 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>91</v>
+        <v>24</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="Q3" s="8"/>
-      <c r="R3" s="14" t="s">
-        <v>451</v>
+      <c r="R3" s="13" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="16">
+        <v>26</v>
+      </c>
+      <c r="B4" s="15">
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>20</v>
@@ -2311,44 +2352,46 @@
       <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P4" s="14"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="16">
+        <v>27</v>
+      </c>
+      <c r="B5" s="15">
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>21</v>
@@ -2356,41 +2399,41 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P5" s="14"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="16">
+        <v>28</v>
+      </c>
+      <c r="B6" s="15">
         <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>21</v>
@@ -2398,38 +2441,38 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P6" s="14"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="16">
+        <v>29</v>
+      </c>
+      <c r="B7" s="15">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>20</v>
@@ -2440,40 +2483,40 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="16">
+        <v>30</v>
+      </c>
+      <c r="B8" s="15">
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>20</v>
@@ -2484,83 +2527,83 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P8" s="14"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="16">
+        <v>31</v>
+      </c>
+      <c r="B9" s="15">
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P9" s="14"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:18" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="16">
+        <v>32</v>
+      </c>
+      <c r="B10" s="15">
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>21</v>
@@ -2568,134 +2611,134 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="P10" s="14"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="14" t="s">
-        <v>451</v>
+      <c r="R10" s="13" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="15">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="7" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="16">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="B12" s="15">
+        <v>10</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>47</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="11" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="16">
-        <v>10</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>48</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>56</v>
+      <c r="I12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
-      <c r="O12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12" s="15"/>
+      <c r="O12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="14"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="8" t="s">
-        <v>461</v>
+      <c r="R12" s="10" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="16">
+        <v>175</v>
+      </c>
+      <c r="B13" s="15">
         <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>20</v>
@@ -2704,13 +2747,13 @@
         <v>21</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>242</v>
+        <v>452</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -2718,7 +2761,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="8"/>
@@ -2726,16 +2769,16 @@
     </row>
     <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" s="16">
+        <v>177</v>
+      </c>
+      <c r="B14" s="15">
         <v>13</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -2744,13 +2787,13 @@
         <v>21</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>243</v>
+        <v>178</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>241</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -2758,7 +2801,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="8"/>
@@ -2766,16 +2809,16 @@
     </row>
     <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="16">
+        <v>179</v>
+      </c>
+      <c r="B15" s="15">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>20</v>
@@ -2784,13 +2827,13 @@
         <v>21</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -2798,7 +2841,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="8"/>
@@ -2806,16 +2849,16 @@
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="16">
+        <v>181</v>
+      </c>
+      <c r="B16" s="15">
         <v>13</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>20</v>
@@ -2824,13 +2867,13 @@
         <v>21</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>245</v>
+        <v>178</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>243</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2838,7 +2881,7 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="8"/>
@@ -2846,16 +2889,16 @@
     </row>
     <row r="17" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="16">
+        <v>182</v>
+      </c>
+      <c r="B17" s="15">
         <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>20</v>
@@ -2864,13 +2907,13 @@
         <v>21</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>430</v>
+        <v>423</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>424</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2878,7 +2921,7 @@
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="O17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="8"/>
@@ -2886,16 +2929,16 @@
     </row>
     <row r="18" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="16">
+        <v>183</v>
+      </c>
+      <c r="B18" s="15">
         <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>20</v>
@@ -2904,13 +2947,13 @@
         <v>21</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>435</v>
+        <v>428</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>429</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -2918,7 +2961,7 @@
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="8"/>
@@ -2926,16 +2969,16 @@
     </row>
     <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="16">
+        <v>184</v>
+      </c>
+      <c r="B19" s="15">
         <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>20</v>
@@ -2944,13 +2987,13 @@
         <v>21</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>246</v>
+        <v>178</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -2958,7 +3001,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="8"/>
@@ -2966,16 +3009,16 @@
     </row>
     <row r="20" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="16">
+        <v>186</v>
+      </c>
+      <c r="B20" s="15">
         <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>20</v>
@@ -2984,13 +3027,13 @@
         <v>21</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>438</v>
+        <v>423</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -2998,7 +3041,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="8"/>
@@ -3006,16 +3049,16 @@
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="16">
+        <v>187</v>
+      </c>
+      <c r="B21" s="15">
         <v>13</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>20</v>
@@ -3024,13 +3067,13 @@
         <v>21</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>247</v>
+        <v>178</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -3038,7 +3081,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="O21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="8"/>
@@ -3046,16 +3089,16 @@
     </row>
     <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B22" s="16">
+        <v>190</v>
+      </c>
+      <c r="B22" s="15">
         <v>13</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>20</v>
@@ -3064,13 +3107,13 @@
         <v>21</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>248</v>
+        <v>178</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -3078,7 +3121,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="8"/>
@@ -3086,16 +3129,16 @@
     </row>
     <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B23" s="16">
+        <v>193</v>
+      </c>
+      <c r="B23" s="15">
         <v>13</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>20</v>
@@ -3104,13 +3147,13 @@
         <v>21</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>249</v>
+        <v>178</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -3118,7 +3161,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="8"/>
@@ -3126,31 +3169,31 @@
     </row>
     <row r="24" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B24" s="16">
+        <v>196</v>
+      </c>
+      <c r="B24" s="15">
         <v>13</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>250</v>
+        <v>178</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3158,7 +3201,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="8"/>
@@ -3166,16 +3209,16 @@
     </row>
     <row r="25" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B25" s="16">
+        <v>199</v>
+      </c>
+      <c r="B25" s="15">
         <v>13</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>20</v>
@@ -3184,13 +3227,13 @@
         <v>21</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>251</v>
+        <v>178</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -3198,7 +3241,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="8"/>
@@ -3206,16 +3249,16 @@
     </row>
     <row r="26" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B26" s="16">
+        <v>202</v>
+      </c>
+      <c r="B26" s="15">
         <v>13</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>20</v>
@@ -3224,13 +3267,13 @@
         <v>21</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>252</v>
+        <v>178</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -3238,7 +3281,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="8"/>
@@ -3246,31 +3289,31 @@
     </row>
     <row r="27" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B27" s="16">
+        <v>204</v>
+      </c>
+      <c r="B27" s="15">
         <v>13</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>253</v>
+        <v>178</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -3278,7 +3321,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="8"/>
@@ -3286,31 +3329,31 @@
     </row>
     <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="15">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B28" s="16">
-        <v>27</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>255</v>
+        <v>210</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -3318,7 +3361,7 @@
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="8"/>
@@ -3326,31 +3369,31 @@
     </row>
     <row r="29" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="16">
+        <v>211</v>
+      </c>
+      <c r="B29" s="15">
         <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>254</v>
+        <v>212</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -3358,7 +3401,7 @@
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="8"/>
@@ -3366,31 +3409,31 @@
     </row>
     <row r="30" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B30" s="16">
+        <v>213</v>
+      </c>
+      <c r="B30" s="15">
         <v>27</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>256</v>
+        <v>214</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
@@ -3398,7 +3441,7 @@
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="8"/>
@@ -3406,31 +3449,31 @@
     </row>
     <row r="31" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B31" s="16">
+        <v>216</v>
+      </c>
+      <c r="B31" s="15">
         <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>257</v>
+        <v>217</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>255</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -3438,7 +3481,7 @@
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="8"/>
@@ -3446,31 +3489,31 @@
     </row>
     <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="16">
+        <v>218</v>
+      </c>
+      <c r="B32" s="15">
         <v>27</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>258</v>
+        <v>219</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -3478,7 +3521,7 @@
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="8"/>
@@ -3486,31 +3529,31 @@
     </row>
     <row r="33" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B33" s="16">
+        <v>221</v>
+      </c>
+      <c r="B33" s="15">
         <v>27</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>259</v>
+        <v>222</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -3518,7 +3561,7 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
       <c r="O33" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="8"/>
@@ -3526,31 +3569,31 @@
     </row>
     <row r="34" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B34" s="16">
+        <v>223</v>
+      </c>
+      <c r="B34" s="15">
         <v>27</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>260</v>
+        <v>224</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -3558,7 +3601,7 @@
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
       <c r="O34" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="8"/>
@@ -3566,16 +3609,16 @@
     </row>
     <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B35" s="16">
+        <v>225</v>
+      </c>
+      <c r="B35" s="15">
         <v>27</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>20</v>
@@ -3584,13 +3627,13 @@
         <v>21</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>261</v>
+        <v>226</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -3598,7 +3641,7 @@
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
       <c r="O35" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="8"/>
@@ -3606,16 +3649,16 @@
     </row>
     <row r="36" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B36" s="16">
+        <v>227</v>
+      </c>
+      <c r="B36" s="15">
         <v>27</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>20</v>
@@ -3624,13 +3667,13 @@
         <v>21</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>262</v>
+        <v>229</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>260</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -3638,7 +3681,7 @@
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
       <c r="O36" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="8"/>
@@ -3646,31 +3689,31 @@
     </row>
     <row r="37" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B37" s="16">
+        <v>231</v>
+      </c>
+      <c r="B37" s="15">
         <v>27</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>396</v>
+        <v>232</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>391</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -3678,7 +3721,7 @@
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
       <c r="O37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="8"/>
@@ -3686,31 +3729,31 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B38" s="16">
+        <v>233</v>
+      </c>
+      <c r="B38" s="15">
         <v>27</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3718,7 +3761,7 @@
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
       <c r="O38" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="8"/>
@@ -3726,31 +3769,31 @@
     </row>
     <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="15">
+        <v>27</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="B39" s="16">
-        <v>27</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>241</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -3758,7 +3801,7 @@
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
       <c r="O39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="8"/>
@@ -3766,16 +3809,16 @@
     </row>
     <row r="40" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B40" s="15">
+        <v>8</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B40" s="16">
-        <v>8</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>20</v>
@@ -3784,61 +3827,61 @@
         <v>21</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Q40" s="8"/>
-      <c r="R40" s="14" t="s">
-        <v>451</v>
+      <c r="R40" s="13" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B41" s="16">
+        <v>278</v>
+      </c>
+      <c r="B41" s="15">
         <v>8</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -3846,7 +3889,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="8"/>
       <c r="O41" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="8"/>
@@ -3854,31 +3897,31 @@
     </row>
     <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B42" s="16">
+        <v>281</v>
+      </c>
+      <c r="B42" s="15">
         <v>8</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -3886,7 +3929,7 @@
       <c r="M42" s="5"/>
       <c r="N42" s="8"/>
       <c r="O42" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="8"/>
@@ -3894,16 +3937,16 @@
     </row>
     <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B43" s="16">
+        <v>284</v>
+      </c>
+      <c r="B43" s="15">
         <v>8</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>20</v>
@@ -3912,13 +3955,13 @@
         <v>21</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
@@ -3926,7 +3969,7 @@
       <c r="M43" s="5"/>
       <c r="N43" s="8"/>
       <c r="O43" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="8"/>
@@ -3934,31 +3977,31 @@
     </row>
     <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="16">
+        <v>288</v>
+      </c>
+      <c r="B44" s="15">
         <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -3966,7 +4009,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="8"/>
       <c r="O44" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="8"/>
@@ -3974,62 +4017,62 @@
     </row>
     <row r="45" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B45" s="16">
+        <v>292</v>
+      </c>
+      <c r="B45" s="15">
         <v>8</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="8"/>
       <c r="O45" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
     </row>
     <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B46" s="15">
+        <v>9</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B46" s="16">
-        <v>9</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>20</v>
@@ -4038,59 +4081,53 @@
         <v>21</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>80</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="P46" s="6"/>
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
     </row>
     <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B47" s="16">
+        <v>300</v>
+      </c>
+      <c r="B47" s="15">
         <v>9</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -4098,7 +4135,7 @@
       <c r="M47" s="5"/>
       <c r="N47" s="8"/>
       <c r="O47" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="8"/>
@@ -4106,16 +4143,16 @@
     </row>
     <row r="48" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B48" s="16">
+        <v>304</v>
+      </c>
+      <c r="B48" s="15">
         <v>9</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>20</v>
@@ -4124,13 +4161,13 @@
         <v>21</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -4138,7 +4175,7 @@
       <c r="M48" s="5"/>
       <c r="N48" s="8"/>
       <c r="O48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="8"/>
@@ -4146,31 +4183,31 @@
     </row>
     <row r="49" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B49" s="16">
+        <v>307</v>
+      </c>
+      <c r="B49" s="15">
         <v>9</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
@@ -4178,7 +4215,7 @@
       <c r="M49" s="5"/>
       <c r="N49" s="8"/>
       <c r="O49" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="8"/>
@@ -4186,31 +4223,31 @@
     </row>
     <row r="50" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B50" s="16">
+        <v>310</v>
+      </c>
+      <c r="B50" s="15">
         <v>9</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
@@ -4218,24 +4255,24 @@
       <c r="M50" s="5"/>
       <c r="N50" s="8"/>
       <c r="O50" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P50" s="6"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
     </row>
-    <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B51" s="16">
-        <v>10</v>
+        <v>490</v>
+      </c>
+      <c r="B51" s="15">
+        <v>16</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>316</v>
+        <v>491</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>20</v>
@@ -4243,54 +4280,60 @@
       <c r="F51" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>180</v>
+      <c r="G51" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>407</v>
+        <v>474</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
+        <v>492</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
-      <c r="N51" s="8"/>
       <c r="O51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="52" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B52" s="16">
+        <v>313</v>
+      </c>
+      <c r="B52" s="15">
         <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -4298,7 +4341,7 @@
       <c r="M52" s="5"/>
       <c r="N52" s="8"/>
       <c r="O52" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P52" s="6"/>
       <c r="Q52" s="8"/>
@@ -4306,31 +4349,31 @@
     </row>
     <row r="53" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B53" s="16">
+        <v>316</v>
+      </c>
+      <c r="B53" s="15">
         <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -4338,7 +4381,7 @@
       <c r="M53" s="5"/>
       <c r="N53" s="8"/>
       <c r="O53" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P53" s="6"/>
       <c r="Q53" s="8"/>
@@ -4346,16 +4389,16 @@
     </row>
     <row r="54" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B54" s="16">
+        <v>319</v>
+      </c>
+      <c r="B54" s="15">
         <v>11</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>20</v>
@@ -4364,13 +4407,13 @@
         <v>21</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
@@ -4378,7 +4421,7 @@
       <c r="M54" s="5"/>
       <c r="N54" s="8"/>
       <c r="O54" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P54" s="6"/>
       <c r="Q54" s="8"/>
@@ -4386,16 +4429,16 @@
     </row>
     <row r="55" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B55" s="16">
+        <v>323</v>
+      </c>
+      <c r="B55" s="15">
         <v>11</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>20</v>
@@ -4404,13 +4447,13 @@
         <v>21</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
@@ -4418,7 +4461,7 @@
       <c r="M55" s="5"/>
       <c r="N55" s="8"/>
       <c r="O55" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="8"/>
@@ -4426,16 +4469,16 @@
     </row>
     <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B56" s="16">
+        <v>325</v>
+      </c>
+      <c r="B56" s="15">
         <v>11</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>20</v>
@@ -4444,13 +4487,13 @@
         <v>21</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
@@ -4458,7 +4501,7 @@
       <c r="M56" s="5"/>
       <c r="N56" s="8"/>
       <c r="O56" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P56" s="6"/>
       <c r="Q56" s="8"/>
@@ -4466,16 +4509,16 @@
     </row>
     <row r="57" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B57" s="16">
+        <v>327</v>
+      </c>
+      <c r="B57" s="15">
         <v>11</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>20</v>
@@ -4484,13 +4527,13 @@
         <v>21</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
@@ -4498,7 +4541,7 @@
       <c r="M57" s="5"/>
       <c r="N57" s="8"/>
       <c r="O57" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="8"/>
@@ -4506,16 +4549,16 @@
     </row>
     <row r="58" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B58" s="16">
+        <v>330</v>
+      </c>
+      <c r="B58" s="15">
         <v>11</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>20</v>
@@ -4524,13 +4567,13 @@
         <v>21</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
@@ -4538,7 +4581,7 @@
       <c r="M58" s="5"/>
       <c r="N58" s="8"/>
       <c r="O58" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="8"/>
@@ -4546,16 +4589,16 @@
     </row>
     <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B59" s="16">
+        <v>333</v>
+      </c>
+      <c r="B59" s="15">
         <v>13</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>20</v>
@@ -4564,13 +4607,13 @@
         <v>21</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
@@ -4578,7 +4621,7 @@
       <c r="M59" s="5"/>
       <c r="N59" s="8"/>
       <c r="O59" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P59" s="6"/>
       <c r="Q59" s="8"/>
@@ -4586,31 +4629,31 @@
     </row>
     <row r="60" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B60" s="16">
+        <v>338</v>
+      </c>
+      <c r="B60" s="15">
         <v>13</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="E60" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
@@ -4618,7 +4661,7 @@
       <c r="M60" s="5"/>
       <c r="N60" s="8"/>
       <c r="O60" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="8"/>
@@ -4626,31 +4669,31 @@
     </row>
     <row r="61" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B61" s="16">
+        <v>341</v>
+      </c>
+      <c r="B61" s="15">
         <v>13</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -4658,7 +4701,7 @@
       <c r="M61" s="5"/>
       <c r="N61" s="8"/>
       <c r="O61" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="8"/>
@@ -4666,31 +4709,31 @@
     </row>
     <row r="62" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B62" s="16">
+        <v>344</v>
+      </c>
+      <c r="B62" s="15">
         <v>17</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
@@ -4698,7 +4741,7 @@
       <c r="M62" s="5"/>
       <c r="N62" s="8"/>
       <c r="O62" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P62" s="6"/>
       <c r="Q62" s="8"/>
@@ -4706,31 +4749,31 @@
     </row>
     <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="B63" s="16">
+        <v>348</v>
+      </c>
+      <c r="B63" s="15">
         <v>17</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
@@ -4738,7 +4781,7 @@
       <c r="M63" s="5"/>
       <c r="N63" s="8"/>
       <c r="O63" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="8"/>
@@ -4746,16 +4789,16 @@
     </row>
     <row r="64" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B64" s="16">
+        <v>351</v>
+      </c>
+      <c r="B64" s="15">
         <v>21</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>20</v>
@@ -4764,13 +4807,13 @@
         <v>21</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -4778,7 +4821,7 @@
       <c r="M64" s="5"/>
       <c r="N64" s="8"/>
       <c r="O64" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P64" s="6"/>
       <c r="Q64" s="8"/>
@@ -4786,31 +4829,31 @@
     </row>
     <row r="65" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B65" s="16">
+        <v>355</v>
+      </c>
+      <c r="B65" s="15">
         <v>21</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
@@ -4818,7 +4861,7 @@
       <c r="M65" s="5"/>
       <c r="N65" s="8"/>
       <c r="O65" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P65" s="6"/>
       <c r="Q65" s="8"/>
@@ -4826,31 +4869,31 @@
     </row>
     <row r="66" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="16">
+        <v>358</v>
+      </c>
+      <c r="B66" s="15">
         <v>21</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
@@ -4858,7 +4901,7 @@
       <c r="M66" s="5"/>
       <c r="N66" s="8"/>
       <c r="O66" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P66" s="6"/>
       <c r="Q66" s="8"/>
@@ -4866,16 +4909,16 @@
     </row>
     <row r="67" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B67" s="16">
+        <v>361</v>
+      </c>
+      <c r="B67" s="15">
         <v>15</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>20</v>
@@ -4884,13 +4927,13 @@
         <v>21</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
@@ -4898,7 +4941,7 @@
       <c r="M67" s="5"/>
       <c r="N67" s="8"/>
       <c r="O67" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P67" s="6"/>
       <c r="Q67" s="8"/>
@@ -4906,16 +4949,16 @@
     </row>
     <row r="68" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="B68" s="16">
+        <v>364</v>
+      </c>
+      <c r="B68" s="15">
         <v>19</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>20</v>
@@ -4924,13 +4967,13 @@
         <v>21</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -4938,7 +4981,7 @@
       <c r="M68" s="5"/>
       <c r="N68" s="8"/>
       <c r="O68" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="8"/>
@@ -4946,31 +4989,31 @@
     </row>
     <row r="69" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B69" s="16">
+        <v>367</v>
+      </c>
+      <c r="B69" s="15">
         <v>19</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
@@ -4978,7 +5021,7 @@
       <c r="M69" s="5"/>
       <c r="N69" s="8"/>
       <c r="O69" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P69" s="6"/>
       <c r="Q69" s="8"/>
@@ -4986,16 +5029,16 @@
     </row>
     <row r="70" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B70" s="16">
+        <v>370</v>
+      </c>
+      <c r="B70" s="15">
         <v>15</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>20</v>
@@ -5004,13 +5047,13 @@
         <v>21</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -5018,7 +5061,7 @@
       <c r="M70" s="5"/>
       <c r="N70" s="8"/>
       <c r="O70" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P70" s="6"/>
       <c r="Q70" s="8"/>
@@ -5026,31 +5069,31 @@
     </row>
     <row r="71" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B71" s="16">
+        <v>373</v>
+      </c>
+      <c r="B71" s="15">
         <v>24</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
@@ -5058,7 +5101,7 @@
       <c r="M71" s="5"/>
       <c r="N71" s="8"/>
       <c r="O71" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P71" s="6"/>
       <c r="Q71" s="8"/>
@@ -5078,7 +5121,7 @@
   <cols>
     <col min="1" max="1" width="12.26953125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="53.6328125" customWidth="1"/>
     <col min="4" max="4" width="16.08984375" customWidth="1"/>
     <col min="5" max="5" width="15.26953125" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" customWidth="1"/>
@@ -5092,28 +5135,28 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -5122,87 +5165,107 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="8"/>
+        <v>455</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
@@ -5215,16 +5278,24 @@
       <c r="H6" s="8"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>449</v>
-      </c>
+      <c r="A8" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>450</v>
-      </c>
+      <c r="A9" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5232,11 +5303,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A87AFD-E38E-4752-8345-B70DBD79E2D9}">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
     <col min="3" max="3" width="21.453125" customWidth="1"/>
     <col min="4" max="4" width="12.54296875" customWidth="1"/>
     <col min="5" max="5" width="10.7265625" customWidth="1"/>
@@ -5249,249 +5320,322 @@
     <col min="12" max="12" width="19.08984375" customWidth="1"/>
     <col min="13" max="13" width="10.54296875" customWidth="1"/>
     <col min="14" max="14" width="23.26953125" customWidth="1"/>
-    <col min="15" max="15" width="26.08984375" customWidth="1"/>
+    <col min="15" max="15" width="23.6328125" customWidth="1"/>
     <col min="16" max="16" width="8.453125" customWidth="1"/>
-    <col min="17" max="17" width="18.54296875" customWidth="1"/>
-    <col min="18" max="18" width="16.90625" customWidth="1"/>
-    <col min="19" max="19" width="23.36328125" customWidth="1"/>
+    <col min="17" max="17" width="14.08984375" customWidth="1"/>
+    <col min="18" max="18" width="12.7265625" customWidth="1"/>
+    <col min="19" max="19" width="14.90625" customWidth="1"/>
     <col min="20" max="20" width="22.90625" customWidth="1"/>
     <col min="21" max="21" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="T1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="T1" s="23" t="s">
+    </row>
+    <row r="2" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="B2" s="7" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>91</v>
+        <v>24</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="L2" s="5">
+        <v>404</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="T2" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" s="5"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>91</v>
+        <v>24</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="L3" s="5">
+        <v>500</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="Q3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R3" s="5"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="5" t="s">
-        <v>484</v>
+        <v>73</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="7" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="L4" s="5">
+        <v>500</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="L5" s="5">
+        <v>500</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="O4" s="5" t="s">
+      <c r="P5" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="T5" s="10" t="s">
         <v>487</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="7" t="s">
-        <v>488</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5510,1180 +5654,1180 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>46366</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0</v>
+      </c>
+      <c r="E2" s="12">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="12">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="12">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="13">
-        <v>2</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0</v>
-      </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0</v>
-      </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
-        <v>0</v>
-      </c>
-      <c r="I3" s="13">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="12">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="13">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="12">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="12">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="12">
+        <v>5</v>
+      </c>
+      <c r="E7" s="12">
+        <v>5</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="12">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="12">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="13">
-        <v>0</v>
-      </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="E8" s="12">
+        <v>3</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="12">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="12">
+        <v>5</v>
+      </c>
+      <c r="E9" s="12">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="13">
-        <v>0</v>
-      </c>
-      <c r="E5" s="13">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="F9" s="12">
+        <v>1</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="12">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="12">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="E10" s="12">
+        <v>4</v>
+      </c>
+      <c r="F10" s="12">
+        <v>1</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="12">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="12">
+        <v>4</v>
+      </c>
+      <c r="E11" s="12">
+        <v>3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>1</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="12">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="13">
+      <c r="E12" s="12">
         <v>5</v>
       </c>
-      <c r="E7" s="13">
+      <c r="F12" s="12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="12">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="12">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12">
+        <v>4</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="12">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="12">
         <v>5</v>
       </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="13">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="13">
-        <v>3</v>
-      </c>
-      <c r="E8" s="13">
-        <v>3</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="13">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="E14" s="12">
         <v>5</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="12">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="12">
+        <v>5</v>
+      </c>
+      <c r="E15" s="12">
         <v>4</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F15" s="12">
         <v>1</v>
       </c>
-      <c r="G9" s="13">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13">
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12">
         <v>1</v>
       </c>
-      <c r="J9" s="13">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="13">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="13">
+      <c r="J15" s="12">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" s="12">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="12">
         <v>5</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E16" s="12">
+        <v>5</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="12">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="12">
+        <v>5</v>
+      </c>
+      <c r="E17" s="12">
         <v>4</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F17" s="12">
         <v>1</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13">
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
         <v>1</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J17" s="12">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="12">
+        <v>17</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="12">
+        <v>4</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="12">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="12">
+        <v>4</v>
+      </c>
+      <c r="E19" s="12">
+        <v>4</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0</v>
+      </c>
+      <c r="I19" s="12">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="12">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="12">
+        <v>4</v>
+      </c>
+      <c r="E20" s="12">
+        <v>4</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="12">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="12">
+        <v>6</v>
+      </c>
+      <c r="E21" s="12">
+        <v>5</v>
+      </c>
+      <c r="F21" s="12">
         <v>1</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" s="13">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="13">
-        <v>4</v>
-      </c>
-      <c r="E11" s="13">
-        <v>3</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12">
         <v>1</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="13">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="13">
-        <v>6</v>
-      </c>
-      <c r="E12" s="13">
-        <v>5</v>
-      </c>
-      <c r="F12" s="13">
-        <v>1</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13">
-        <v>1</v>
-      </c>
-      <c r="J12" s="13">
-        <v>0</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="13">
-        <v>12</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="13">
-        <v>4</v>
-      </c>
-      <c r="E13" s="13">
-        <v>4</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="13">
-        <v>13</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="13">
-        <v>5</v>
-      </c>
-      <c r="E14" s="13">
-        <v>5</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B15" s="13">
-        <v>14</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="13">
-        <v>5</v>
-      </c>
-      <c r="E15" s="13">
-        <v>4</v>
-      </c>
-      <c r="F15" s="13">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <v>1</v>
-      </c>
-      <c r="J15" s="13">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="13">
-        <v>15</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="13">
-        <v>5</v>
-      </c>
-      <c r="E16" s="13">
-        <v>5</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <v>0</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="13">
-        <v>16</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="13">
-        <v>5</v>
-      </c>
-      <c r="E17" s="13">
-        <v>4</v>
-      </c>
-      <c r="F17" s="13">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>1</v>
-      </c>
-      <c r="J17" s="13">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" s="13">
-        <v>17</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="13">
-        <v>4</v>
-      </c>
-      <c r="E18" s="13">
-        <v>4</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="13">
-        <v>18</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="13">
-        <v>4</v>
-      </c>
-      <c r="E19" s="13">
-        <v>4</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="15" t="s">
+      <c r="J21" s="12">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="B20" s="13">
-        <v>19</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="13">
-        <v>4</v>
-      </c>
-      <c r="E20" s="13">
-        <v>4</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="13">
-        <v>20</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="13">
-        <v>6</v>
-      </c>
-      <c r="E21" s="13">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="13">
-        <v>1</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>46032</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="12">
         <v>21</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="13">
+        <v>84</v>
+      </c>
+      <c r="D22" s="12">
         <v>4</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <v>3</v>
       </c>
-      <c r="F22" s="13">
-        <v>0</v>
-      </c>
-      <c r="G22" s="13">
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
         <v>1</v>
       </c>
-      <c r="H22" s="13">
-        <v>0</v>
-      </c>
-      <c r="I22" s="13">
+      <c r="H22" s="12">
+        <v>0</v>
+      </c>
+      <c r="I22" s="12">
         <v>1</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="12">
         <v>0</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>46064</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="12">
         <v>22</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="13">
+        <v>84</v>
+      </c>
+      <c r="D23" s="12">
         <v>4</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <v>4</v>
       </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="13">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
-        <v>0</v>
-      </c>
-      <c r="I23" s="13">
-        <v>0</v>
-      </c>
-      <c r="J23" s="13">
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12">
         <v>0</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>46092</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="12">
         <v>23</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="13">
+        <v>84</v>
+      </c>
+      <c r="D24" s="12">
         <v>4</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <v>4</v>
       </c>
-      <c r="F24" s="13">
-        <v>0</v>
-      </c>
-      <c r="G24" s="13">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13">
-        <v>0</v>
-      </c>
-      <c r="I24" s="13">
-        <v>0</v>
-      </c>
-      <c r="J24" s="13">
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>46123</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="12">
         <v>24</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="13">
+        <v>84</v>
+      </c>
+      <c r="D25" s="12">
         <v>5</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <v>4</v>
       </c>
-      <c r="F25" s="13">
-        <v>0</v>
-      </c>
-      <c r="G25" s="13">
+      <c r="F25" s="12">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
         <v>1</v>
       </c>
-      <c r="H25" s="13">
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
+      <c r="H25" s="12">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12">
         <v>0</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>46153</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="12">
         <v>25</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="13">
+        <v>84</v>
+      </c>
+      <c r="D26" s="12">
         <v>4</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <v>4</v>
       </c>
-      <c r="F26" s="13">
-        <v>0</v>
-      </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13">
-        <v>0</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
+      <c r="F26" s="12">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12">
         <v>0</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>46184</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="12">
         <v>26</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="13">
+        <v>84</v>
+      </c>
+      <c r="D27" s="12">
         <v>9</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <v>7</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="12">
         <v>2</v>
       </c>
-      <c r="G27" s="13">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13">
-        <v>0</v>
-      </c>
-      <c r="I27" s="13">
+      <c r="G27" s="12">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12">
         <v>2</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="12">
         <v>1</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>46214</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <v>27</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="13">
+        <v>84</v>
+      </c>
+      <c r="D28" s="12">
         <v>6</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <v>6</v>
       </c>
-      <c r="F28" s="13">
-        <v>0</v>
-      </c>
-      <c r="G28" s="13">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13">
-        <v>0</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12">
         <v>0</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>46245</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="12">
         <v>28</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="13">
+        <v>84</v>
+      </c>
+      <c r="D29" s="12">
         <v>4</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <v>4</v>
       </c>
-      <c r="F29" s="13">
-        <v>0</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
-        <v>0</v>
-      </c>
-      <c r="I29" s="13">
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
+      <c r="F29" s="12">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12">
+        <v>0</v>
+      </c>
+      <c r="I29" s="12">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12">
         <v>0</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>46276</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="12">
         <v>29</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="13">
+        <v>84</v>
+      </c>
+      <c r="D30" s="12">
         <v>5</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <v>5</v>
       </c>
-      <c r="F30" s="13">
-        <v>0</v>
-      </c>
-      <c r="G30" s="13">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13">
-        <v>0</v>
-      </c>
-      <c r="I30" s="13">
-        <v>0</v>
-      </c>
-      <c r="J30" s="13">
+      <c r="F30" s="12">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12">
         <v>0</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>46306</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="12">
         <v>30</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="13">
+        <v>84</v>
+      </c>
+      <c r="D31" s="12">
         <v>6</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <v>6</v>
       </c>
-      <c r="F31" s="13">
-        <v>0</v>
-      </c>
-      <c r="G31" s="13">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13">
-        <v>0</v>
-      </c>
-      <c r="I31" s="13">
-        <v>0</v>
-      </c>
-      <c r="J31" s="13">
+      <c r="F31" s="12">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12">
+        <v>0</v>
+      </c>
+      <c r="I31" s="12">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12">
         <v>0</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -6709,317 +6853,317 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="13">
+        <v>35</v>
+      </c>
+      <c r="B2" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A2)</f>
         <v>11</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"PASS")</f>
         <v>11</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A2,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <f>IFERROR(C2/B2,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="13">
+        <v>165</v>
+      </c>
+      <c r="B3" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A3)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A3,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <f t="shared" ref="F3:F13" si="0">IF(B3=0,0,C3/B3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="13">
+        <v>166</v>
+      </c>
+      <c r="B4" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A4,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="13">
+        <v>167</v>
+      </c>
+      <c r="B5" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A5,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="13">
+        <v>168</v>
+      </c>
+      <c r="B6" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A6,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="13">
+        <v>169</v>
+      </c>
+      <c r="B7" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A7,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="13">
+        <v>170</v>
+      </c>
+      <c r="B8" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A8)</f>
         <v>5</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A8,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="13">
+        <v>171</v>
+      </c>
+      <c r="B9" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A9,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="13">
+        <v>172</v>
+      </c>
+      <c r="B10" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A10,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="13">
+        <v>173</v>
+      </c>
+      <c r="B11" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A11,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="13">
+        <v>152</v>
+      </c>
+      <c r="B12" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A12,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="13">
+        <v>174</v>
+      </c>
+      <c r="B13" s="12">
         <f>COUNTIF(MASTER_TC!C:C,A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>COUNTIFS(MASTER_TC!C:C,A13,MASTER_TC!K:K,"BLOCKED")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/docs/qa/01_Master_Test_Cases.xlsx
+++ b/docs/qa/01_Master_Test_Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75382754-465F-445A-8E27-053E2EACCA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AC47B6-1A67-4FAF-BCFA-FE56EA34FA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11235" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3971,11 +3971,11 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9751,7 +9751,7 @@
       <c r="J112" t="s">
         <v>1074</v>
       </c>
-      <c r="K112" s="60" t="s">
+      <c r="K112" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L112" t="s">
@@ -9767,7 +9767,7 @@
       <c r="O112" t="s">
         <v>404</v>
       </c>
-      <c r="P112" s="59">
+      <c r="P112" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       <c r="J113" t="s">
         <v>1082</v>
       </c>
-      <c r="K113" s="60" t="s">
+      <c r="K113" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L113" t="s">
@@ -9818,7 +9818,7 @@
       <c r="O113" t="s">
         <v>404</v>
       </c>
-      <c r="P113" s="59">
+      <c r="P113" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       <c r="J114" t="s">
         <v>1090</v>
       </c>
-      <c r="K114" s="60" t="s">
+      <c r="K114" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L114" t="s">
@@ -9869,7 +9869,7 @@
       <c r="O114" t="s">
         <v>404</v>
       </c>
-      <c r="P114" s="59">
+      <c r="P114" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
       <c r="J115" t="s">
         <v>1096</v>
       </c>
-      <c r="K115" s="60" t="s">
+      <c r="K115" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L115" t="s">
@@ -9920,7 +9920,7 @@
       <c r="O115" t="s">
         <v>404</v>
       </c>
-      <c r="P115" s="59">
+      <c r="P115" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       <c r="J116" t="s">
         <v>1102</v>
       </c>
-      <c r="K116" s="60" t="s">
+      <c r="K116" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L116" t="s">
@@ -9971,7 +9971,7 @@
       <c r="O116" t="s">
         <v>404</v>
       </c>
-      <c r="P116" s="59">
+      <c r="P116" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       <c r="J117" t="s">
         <v>1111</v>
       </c>
-      <c r="K117" s="60" t="s">
+      <c r="K117" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L117" t="s">
@@ -10022,7 +10022,7 @@
       <c r="O117" t="s">
         <v>404</v>
       </c>
-      <c r="P117" s="59">
+      <c r="P117" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -10057,7 +10057,7 @@
       <c r="J118" t="s">
         <v>1117</v>
       </c>
-      <c r="K118" s="60" t="s">
+      <c r="K118" s="59" t="s">
         <v>27</v>
       </c>
       <c r="L118" t="s">
@@ -10073,7 +10073,7 @@
       <c r="O118" t="s">
         <v>404</v>
       </c>
-      <c r="P118" s="59">
+      <c r="P118" s="58">
         <v>46322</v>
       </c>
     </row>
@@ -10158,9 +10158,16 @@
     <hyperlink ref="N70" r:id="rId77" xr:uid="{8D48B14F-5B96-4013-BF36-44D8E733794C}"/>
     <hyperlink ref="N71" r:id="rId78" xr:uid="{EEDC24C4-D93D-4655-9461-D8AF36FD26DB}"/>
     <hyperlink ref="N72" r:id="rId79" xr:uid="{12D4C9A3-6BC5-4A52-9045-6452F292C102}"/>
+    <hyperlink ref="N112" r:id="rId80" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-001_network-throttling-3g-dashboard-kpi.png" display="2026-10-27_Hari-16_TC-H16-001_network-throttling-3g-dashboard-kpi.png" xr:uid="{D2E10ECA-370A-4755-924F-2F1045EB1D52}"/>
+    <hyperlink ref="N113" r:id="rId81" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-002_mobile-viewport-dashboard-kpi-layout.png" display="2026-10-27_Hari-16_TC-H16-002_mobile-viewport-dashboard-kpi-layout.png" xr:uid="{FB8B339B-20A5-4002-97C5-D5742F4A818A}"/>
+    <hyperlink ref="N114" r:id="rId82" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-003_mobile-user-profile-account-switcher-dropdown.png" display="2026-10-27_Hari-16_TC-H16-003_mobile-user-profile-account-switcher-dropdown.png" xr:uid="{6DC4682A-9EAE-4FB0-8FE5-5A658795C9FC}"/>
+    <hyperlink ref="N115" r:id="rId83" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-004_mobile-devices-table-horizontal-swipe-scroll.png" display="2026-10-27_Hari-16_TC-H16-004_mobile-devices-table-horizontal-swipe-scroll.png" xr:uid="{3AD0BED5-2196-4F20-9680-EC1A358472D8}"/>
+    <hyperlink ref="N116" r:id="rId84" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-005_mobile-devices-table-full-inventory-rendering.png" display="2026-10-27_Hari-16_TC-H16-005_mobile-devices-table-full-inventory-rendering.png" xr:uid="{FB35E71A-BBA2-4B7C-9E8C-8B6E5A928B7F}"/>
+    <hyperlink ref="N117" r:id="rId85" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-006_backend-api-error-sanitization-404-zero-leakage.png" display="2026-10-27_Hari-16_TC-H16-006_backend-api-error-sanitization-404-zero-leakage.png" xr:uid="{253B4AC1-DF7F-427D-B133-59ED61B392E3}"/>
+    <hyperlink ref="N118" r:id="rId86" tooltip="Klik untuk membuka bukti screenshot 2026-10-27_Hari-16_TC-H16-007_device-keyword-search-cctv-filter-integrity.png" display="2026-10-27_Hari-16_TC-H16-007_device-keyword-search-cctv-filter-integrity.png" xr:uid="{ACDEFD5D-3794-41C9-827A-EFC720AC1F87}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId80"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId87"/>
 </worksheet>
 </file>
 
@@ -10509,19 +10516,19 @@
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="60" t="s">
         <v>789</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
       <c r="M13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="60" t="s">
         <v>790</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
       <c r="M14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.25">
